--- a/research/traditional_assets/database/data/germany/germany_utility_water.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_utility_water.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06417717306941925</v>
+        <v>0.06401614155021099</v>
       </c>
       <c r="C2">
-        <v>80.89812019626326</v>
+        <v>80.12350643930094</v>
       </c>
       <c r="D2">
-        <v>48.99812019626327</v>
+        <v>49.04350643930093</v>
       </c>
       <c r="E2">
-        <v>-24.9</v>
+        <v>-24.08</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="G2">
         <v>31.9</v>
@@ -1445,28 +1445,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.041246</v>
       </c>
       <c r="N2">
-        <v>6.739999999999999</v>
+        <v>6.698753999999999</v>
       </c>
       <c r="O2">
-        <v>2.022</v>
+        <v>2.0096262</v>
       </c>
       <c r="P2">
-        <v>4.718</v>
+        <v>4.6891278</v>
       </c>
       <c r="Q2">
-        <v>9.577999999999999</v>
+        <v>9.549127800000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06417717306941925</v>
+        <v>0.0643071126769808</v>
       </c>
       <c r="T2">
-        <v>0.4244150824346248</v>
+        <v>0.42741599715891</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>163.4097851912913</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06401614155021099</v>
+        <v>0.06385511003100275</v>
       </c>
       <c r="C3">
-        <v>80.12350643930094</v>
+        <v>79.34897684152197</v>
       </c>
       <c r="D3">
-        <v>49.04350643930093</v>
+        <v>49.08897684152198</v>
       </c>
       <c r="E3">
-        <v>-24.08</v>
+        <v>-23.26</v>
       </c>
       <c r="F3">
-        <v>0.8200000000000001</v>
+        <v>1.64</v>
       </c>
       <c r="G3">
         <v>31.9</v>
@@ -1527,28 +1527,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M3">
-        <v>0.041246</v>
+        <v>0.082492</v>
       </c>
       <c r="N3">
-        <v>6.698753999999999</v>
+        <v>6.657507999999999</v>
       </c>
       <c r="O3">
-        <v>2.0096262</v>
+        <v>1.9972524</v>
       </c>
       <c r="P3">
-        <v>4.6891278</v>
+        <v>4.660255599999999</v>
       </c>
       <c r="Q3">
-        <v>9.549127800000001</v>
+        <v>9.520255599999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0643071126769808</v>
+        <v>0.0644397041132681</v>
       </c>
       <c r="T3">
-        <v>0.42741599715891</v>
+        <v>0.4304781550408338</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>163.4097851912913</v>
+        <v>81.70489259564563</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06385511003100275</v>
+        <v>0.06369407851179447</v>
       </c>
       <c r="C4">
-        <v>79.34897684152197</v>
+        <v>78.57453163722677</v>
       </c>
       <c r="D4">
-        <v>49.08897684152198</v>
+        <v>49.13453163722676</v>
       </c>
       <c r="E4">
-        <v>-23.26</v>
+        <v>-22.44</v>
       </c>
       <c r="F4">
-        <v>1.64</v>
+        <v>2.46</v>
       </c>
       <c r="G4">
         <v>31.9</v>
@@ -1609,28 +1609,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M4">
-        <v>0.082492</v>
+        <v>0.123738</v>
       </c>
       <c r="N4">
-        <v>6.657507999999999</v>
+        <v>6.616261999999999</v>
       </c>
       <c r="O4">
-        <v>1.9972524</v>
+        <v>1.9848786</v>
       </c>
       <c r="P4">
-        <v>4.660255599999999</v>
+        <v>4.631383399999999</v>
       </c>
       <c r="Q4">
-        <v>9.520255599999999</v>
+        <v>9.4913834</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0644397041132681</v>
+        <v>0.06457502939360255</v>
       </c>
       <c r="T4">
-        <v>0.4304781550408338</v>
+        <v>0.4336034501986734</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>81.70489259564563</v>
+        <v>54.46992839709709</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06369407851179447</v>
+        <v>0.06353304699258622</v>
       </c>
       <c r="C5">
-        <v>78.57453163722677</v>
+        <v>77.8001710615861</v>
       </c>
       <c r="D5">
-        <v>49.13453163722676</v>
+        <v>49.18017106158611</v>
       </c>
       <c r="E5">
-        <v>-22.44</v>
+        <v>-21.62</v>
       </c>
       <c r="F5">
-        <v>2.46</v>
+        <v>3.28</v>
       </c>
       <c r="G5">
         <v>31.9</v>
@@ -1691,28 +1691,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M5">
-        <v>0.123738</v>
+        <v>0.164984</v>
       </c>
       <c r="N5">
-        <v>6.616261999999999</v>
+        <v>6.575016</v>
       </c>
       <c r="O5">
-        <v>1.9848786</v>
+        <v>1.9725048</v>
       </c>
       <c r="P5">
-        <v>4.631383399999999</v>
+        <v>4.6025112</v>
       </c>
       <c r="Q5">
-        <v>9.4913834</v>
+        <v>9.462511200000002</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06457502939360255</v>
+        <v>0.06471317395061064</v>
       </c>
       <c r="T5">
-        <v>0.4336034501986734</v>
+        <v>0.4367938556723013</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>54.46992839709709</v>
+        <v>40.85244629782282</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06353304699258622</v>
+        <v>0.06337201547337797</v>
       </c>
       <c r="C6">
-        <v>77.8001710615861</v>
+        <v>77.02589535064547</v>
       </c>
       <c r="D6">
-        <v>49.18017106158611</v>
+        <v>49.22589535064547</v>
       </c>
       <c r="E6">
-        <v>-21.62</v>
+        <v>-20.8</v>
       </c>
       <c r="F6">
-        <v>3.28</v>
+        <v>4.100000000000001</v>
       </c>
       <c r="G6">
         <v>31.9</v>
@@ -1773,28 +1773,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M6">
-        <v>0.164984</v>
+        <v>0.20623</v>
       </c>
       <c r="N6">
-        <v>6.575016</v>
+        <v>6.53377</v>
       </c>
       <c r="O6">
-        <v>1.9725048</v>
+        <v>1.960131</v>
       </c>
       <c r="P6">
-        <v>4.6025112</v>
+        <v>4.573639</v>
       </c>
       <c r="Q6">
-        <v>9.462511200000002</v>
+        <v>9.433638999999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06471317395061064</v>
+        <v>0.06485422681408207</v>
       </c>
       <c r="T6">
-        <v>0.4367938556723013</v>
+        <v>0.4400514275769531</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.85244629782282</v>
+        <v>32.68195703825825</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06337201547337797</v>
+        <v>0.0632109839541697</v>
       </c>
       <c r="C7">
-        <v>77.02589535064547</v>
+        <v>76.25170474132894</v>
       </c>
       <c r="D7">
-        <v>49.22589535064547</v>
+        <v>49.27170474132893</v>
       </c>
       <c r="E7">
-        <v>-20.8</v>
+        <v>-19.98</v>
       </c>
       <c r="F7">
-        <v>4.100000000000001</v>
+        <v>4.920000000000001</v>
       </c>
       <c r="G7">
         <v>31.9</v>
@@ -1855,28 +1855,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M7">
-        <v>0.20623</v>
+        <v>0.247476</v>
       </c>
       <c r="N7">
-        <v>6.53377</v>
+        <v>6.492524</v>
       </c>
       <c r="O7">
-        <v>1.960131</v>
+        <v>1.9477572</v>
       </c>
       <c r="P7">
-        <v>4.573639</v>
+        <v>4.5447668</v>
       </c>
       <c r="Q7">
-        <v>9.433638999999999</v>
+        <v>9.404766800000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06485422681408207</v>
+        <v>0.0649982808023082</v>
       </c>
       <c r="T7">
-        <v>0.4400514275769531</v>
+        <v>0.4433783095221293</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.68195703825825</v>
+        <v>27.23496419854854</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0632109839541697</v>
+        <v>0.06304995243496146</v>
       </c>
       <c r="C8">
-        <v>76.25170474132894</v>
+        <v>75.47759947144334</v>
       </c>
       <c r="D8">
-        <v>49.27170474132893</v>
+        <v>49.31759947144334</v>
       </c>
       <c r="E8">
-        <v>-19.98</v>
+        <v>-19.16</v>
       </c>
       <c r="F8">
-        <v>4.92</v>
+        <v>5.739999999999999</v>
       </c>
       <c r="G8">
         <v>31.9</v>
@@ -1937,28 +1937,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M8">
-        <v>0.247476</v>
+        <v>0.288722</v>
       </c>
       <c r="N8">
-        <v>6.492524</v>
+        <v>6.451277999999999</v>
       </c>
       <c r="O8">
-        <v>1.9477572</v>
+        <v>1.9353834</v>
       </c>
       <c r="P8">
-        <v>4.5447668</v>
+        <v>4.515894599999999</v>
       </c>
       <c r="Q8">
-        <v>9.404766800000001</v>
+        <v>9.375894599999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0649982808023082</v>
+        <v>0.06514543272576501</v>
       </c>
       <c r="T8">
-        <v>0.4433783095221293</v>
+        <v>0.446776737315589</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.23496419854855</v>
+        <v>23.34425502732732</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06304995243496145</v>
+        <v>0.0628889209157532</v>
       </c>
       <c r="C9">
-        <v>75.47759947144334</v>
+        <v>74.70357977968239</v>
       </c>
       <c r="D9">
-        <v>49.31759947144334</v>
+        <v>49.36357977968239</v>
       </c>
       <c r="E9">
-        <v>-19.16</v>
+        <v>-18.34</v>
       </c>
       <c r="F9">
-        <v>5.74</v>
+        <v>6.56</v>
       </c>
       <c r="G9">
         <v>31.9</v>
@@ -2019,28 +2019,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M9">
-        <v>0.288722</v>
+        <v>0.329968</v>
       </c>
       <c r="N9">
-        <v>6.451277999999999</v>
+        <v>6.410031999999999</v>
       </c>
       <c r="O9">
-        <v>1.9353834</v>
+        <v>1.9230096</v>
       </c>
       <c r="P9">
-        <v>4.515894599999999</v>
+        <v>4.4870224</v>
       </c>
       <c r="Q9">
-        <v>9.375894599999999</v>
+        <v>9.3470224</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06514543272576501</v>
+        <v>0.06529578360407956</v>
       </c>
       <c r="T9">
-        <v>0.446776737315589</v>
+        <v>0.4502490439741238</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.34425502732732</v>
+        <v>20.42622314891141</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0628889209157532</v>
+        <v>0.06272788939654493</v>
       </c>
       <c r="C10">
-        <v>74.70357977968239</v>
+        <v>73.92964590563076</v>
       </c>
       <c r="D10">
-        <v>49.36357977968239</v>
+        <v>49.40964590563077</v>
       </c>
       <c r="E10">
-        <v>-18.34</v>
+        <v>-17.52</v>
       </c>
       <c r="F10">
-        <v>6.56</v>
+        <v>7.38</v>
       </c>
       <c r="G10">
         <v>31.9</v>
@@ -2101,28 +2101,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M10">
-        <v>0.329968</v>
+        <v>0.371214</v>
       </c>
       <c r="N10">
-        <v>6.410031999999999</v>
+        <v>6.368785999999999</v>
       </c>
       <c r="O10">
-        <v>1.9230096</v>
+        <v>1.9106358</v>
       </c>
       <c r="P10">
-        <v>4.4870224</v>
+        <v>4.4581502</v>
       </c>
       <c r="Q10">
-        <v>9.3470224</v>
+        <v>9.3181502</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06529578360407956</v>
+        <v>0.06544943889730212</v>
       </c>
       <c r="T10">
-        <v>0.4502490439741238</v>
+        <v>0.4537976650647143</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.42622314891141</v>
+        <v>18.15664279903236</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06272788939654493</v>
+        <v>0.06256685787733667</v>
       </c>
       <c r="C11">
-        <v>73.92964590563076</v>
+        <v>73.15579808976831</v>
       </c>
       <c r="D11">
-        <v>49.40964590563077</v>
+        <v>49.45579808976832</v>
       </c>
       <c r="E11">
-        <v>-17.52</v>
+        <v>-16.7</v>
       </c>
       <c r="F11">
-        <v>7.38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G11">
         <v>31.9</v>
@@ -2183,28 +2183,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M11">
-        <v>0.371214</v>
+        <v>0.4124599999999999</v>
       </c>
       <c r="N11">
-        <v>6.368785999999999</v>
+        <v>6.327539999999999</v>
       </c>
       <c r="O11">
-        <v>1.9106358</v>
+        <v>1.898262</v>
       </c>
       <c r="P11">
-        <v>4.4581502</v>
+        <v>4.429277999999999</v>
       </c>
       <c r="Q11">
-        <v>9.3181502</v>
+        <v>9.289277999999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06544943889730212</v>
+        <v>0.0656065087525963</v>
       </c>
       <c r="T11">
-        <v>0.4537976650647143</v>
+        <v>0.4574251444017623</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.15664279903236</v>
+        <v>16.34097851912913</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06256685787733667</v>
+        <v>0.06240582635812841</v>
       </c>
       <c r="C12">
-        <v>73.15579808976831</v>
+        <v>72.38203657347425</v>
       </c>
       <c r="D12">
-        <v>49.45579808976832</v>
+        <v>49.50203657347424</v>
       </c>
       <c r="E12">
-        <v>-16.7</v>
+        <v>-15.88</v>
       </c>
       <c r="F12">
-        <v>8.200000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="G12">
         <v>31.9</v>
@@ -2265,28 +2265,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M12">
-        <v>0.41246</v>
+        <v>0.4537059999999999</v>
       </c>
       <c r="N12">
-        <v>6.327539999999999</v>
+        <v>6.286294</v>
       </c>
       <c r="O12">
-        <v>1.898262</v>
+        <v>1.8858882</v>
       </c>
       <c r="P12">
-        <v>4.429277999999999</v>
+        <v>4.4004058</v>
       </c>
       <c r="Q12">
-        <v>9.289277999999999</v>
+        <v>9.260405800000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0656065087525963</v>
+        <v>0.06576710826756002</v>
       </c>
       <c r="T12">
-        <v>0.4574251444017623</v>
+        <v>0.461134140128407</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.34097851912912</v>
+        <v>14.85543501739012</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06240582635812841</v>
+        <v>0.06224479483892015</v>
       </c>
       <c r="C13">
-        <v>72.38203657347425</v>
+        <v>71.60836159903127</v>
       </c>
       <c r="D13">
-        <v>49.50203657347424</v>
+        <v>49.54836159903127</v>
       </c>
       <c r="E13">
-        <v>-15.88</v>
+        <v>-15.06</v>
       </c>
       <c r="F13">
-        <v>9.02</v>
+        <v>9.84</v>
       </c>
       <c r="G13">
         <v>31.9</v>
@@ -2347,28 +2347,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M13">
-        <v>0.4537059999999999</v>
+        <v>0.4949519999999999</v>
       </c>
       <c r="N13">
-        <v>6.286294</v>
+        <v>6.245048</v>
       </c>
       <c r="O13">
-        <v>1.8858882</v>
+        <v>1.8735144</v>
       </c>
       <c r="P13">
-        <v>4.4004058</v>
+        <v>4.371533599999999</v>
       </c>
       <c r="Q13">
-        <v>9.260405800000001</v>
+        <v>9.231533599999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.06576710826756002</v>
+        <v>0.06593135777150018</v>
       </c>
       <c r="T13">
-        <v>0.461134140128407</v>
+        <v>0.4649274312124754</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.85543501739012</v>
+        <v>13.61748209927427</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06224479483892015</v>
+        <v>0.0622202633197119</v>
       </c>
       <c r="C14">
-        <v>71.60836159903127</v>
+        <v>70.79542635836879</v>
       </c>
       <c r="D14">
-        <v>49.54836159903127</v>
+        <v>49.55542635836879</v>
       </c>
       <c r="E14">
-        <v>-15.06</v>
+        <v>-14.24</v>
       </c>
       <c r="F14">
-        <v>9.84</v>
+        <v>10.66</v>
       </c>
       <c r="G14">
         <v>31.9</v>
@@ -2429,45 +2429,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M14">
-        <v>0.4949519999999999</v>
+        <v>0.552188</v>
       </c>
       <c r="N14">
-        <v>6.245048</v>
+        <v>6.187811999999999</v>
       </c>
       <c r="O14">
-        <v>1.8735144</v>
+        <v>1.8563436</v>
       </c>
       <c r="P14">
-        <v>4.371533599999999</v>
+        <v>4.331468399999999</v>
       </c>
       <c r="Q14">
-        <v>9.231533599999999</v>
+        <v>9.1914684</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.06593135777150018</v>
+        <v>0.06609938312610564</v>
       </c>
       <c r="T14">
-        <v>0.4649274312124754</v>
+        <v>0.4688079243904304</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.61748209927427</v>
+        <v>12.20598781574391</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0622202633197119</v>
+        <v>0.06206973180050365</v>
       </c>
       <c r="C15">
-        <v>70.79542635836879</v>
+        <v>70.01882163214985</v>
       </c>
       <c r="D15">
-        <v>49.55542635836879</v>
+        <v>49.59882163214986</v>
       </c>
       <c r="E15">
-        <v>-14.24</v>
+        <v>-13.42</v>
       </c>
       <c r="F15">
-        <v>10.66</v>
+        <v>11.48</v>
       </c>
       <c r="G15">
         <v>31.9</v>
@@ -2511,28 +2511,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M15">
-        <v>0.552188</v>
+        <v>0.594664</v>
       </c>
       <c r="N15">
-        <v>6.187811999999999</v>
+        <v>6.145335999999999</v>
       </c>
       <c r="O15">
-        <v>1.8563436</v>
+        <v>1.8436008</v>
       </c>
       <c r="P15">
-        <v>4.331468399999999</v>
+        <v>4.3017352</v>
       </c>
       <c r="Q15">
-        <v>9.1914684</v>
+        <v>9.161735199999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.06609938312610564</v>
+        <v>0.06627131604709727</v>
       </c>
       <c r="T15">
-        <v>0.4688079243904304</v>
+        <v>0.4727786615957797</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.20598781574391</v>
+        <v>11.33413154319078</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06206973180050365</v>
+        <v>0.06191920028129538</v>
       </c>
       <c r="C16">
-        <v>70.01882163214985</v>
+        <v>69.2422929743024</v>
       </c>
       <c r="D16">
-        <v>49.59882163214986</v>
+        <v>49.64229297430241</v>
       </c>
       <c r="E16">
-        <v>-13.42</v>
+        <v>-12.6</v>
       </c>
       <c r="F16">
-        <v>11.48</v>
+        <v>12.3</v>
       </c>
       <c r="G16">
         <v>31.9</v>
@@ -2593,28 +2593,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M16">
-        <v>0.594664</v>
+        <v>0.6371400000000002</v>
       </c>
       <c r="N16">
-        <v>6.145335999999999</v>
+        <v>6.102859999999999</v>
       </c>
       <c r="O16">
-        <v>1.8436008</v>
+        <v>1.830858</v>
       </c>
       <c r="P16">
-        <v>4.3017352</v>
+        <v>4.272001999999999</v>
       </c>
       <c r="Q16">
-        <v>9.161735199999999</v>
+        <v>9.132002</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.06627131604709727</v>
+        <v>0.0664472944485828</v>
       </c>
       <c r="T16">
-        <v>0.4727786615957797</v>
+        <v>0.4768428279118432</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.33413154319078</v>
+        <v>10.57852277364472</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06191920028129538</v>
+        <v>0.06176866876208712</v>
       </c>
       <c r="C17">
-        <v>69.2422929743024</v>
+        <v>68.46584058501435</v>
       </c>
       <c r="D17">
-        <v>49.64229297430241</v>
+        <v>49.68584058501435</v>
       </c>
       <c r="E17">
-        <v>-12.6</v>
+        <v>-11.78</v>
       </c>
       <c r="F17">
-        <v>12.3</v>
+        <v>13.12</v>
       </c>
       <c r="G17">
         <v>31.9</v>
@@ -2675,28 +2675,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M17">
-        <v>0.6371399999999999</v>
+        <v>0.679616</v>
       </c>
       <c r="N17">
-        <v>6.10286</v>
+        <v>6.060383999999999</v>
       </c>
       <c r="O17">
-        <v>1.830858</v>
+        <v>1.8181152</v>
       </c>
       <c r="P17">
-        <v>4.272002</v>
+        <v>4.2422688</v>
       </c>
       <c r="Q17">
-        <v>9.132002</v>
+        <v>9.102268800000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0664472944485828</v>
+        <v>0.06662746281200849</v>
       </c>
       <c r="T17">
-        <v>0.4768428279118432</v>
+        <v>0.4810037600925748</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.57852277364472</v>
+        <v>9.917365100291928</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06176866876208712</v>
+        <v>0.06182043724287887</v>
       </c>
       <c r="C18">
-        <v>68.46584058501435</v>
+        <v>67.63085574479726</v>
       </c>
       <c r="D18">
-        <v>49.68584058501435</v>
+        <v>49.67085574479725</v>
       </c>
       <c r="E18">
-        <v>-11.78</v>
+        <v>-10.96</v>
       </c>
       <c r="F18">
-        <v>13.12</v>
+        <v>13.94</v>
       </c>
       <c r="G18">
         <v>31.9</v>
@@ -2757,45 +2757,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M18">
-        <v>0.679616</v>
+        <v>0.7457900000000001</v>
       </c>
       <c r="N18">
-        <v>6.060383999999999</v>
+        <v>5.994209999999999</v>
       </c>
       <c r="O18">
-        <v>1.8181152</v>
+        <v>1.798263</v>
       </c>
       <c r="P18">
-        <v>4.2422688</v>
+        <v>4.195946999999999</v>
       </c>
       <c r="Q18">
-        <v>9.102268800000001</v>
+        <v>9.055947</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.06662746281200849</v>
+        <v>0.06681197258178177</v>
       </c>
       <c r="T18">
-        <v>0.4810037600925748</v>
+        <v>0.4852649556993482</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.917365100291928</v>
+        <v>9.037396586170367</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06182043724287887</v>
+        <v>0.06168180572367062</v>
       </c>
       <c r="C19">
-        <v>67.63085574479726</v>
+        <v>66.85100417537585</v>
       </c>
       <c r="D19">
-        <v>49.67085574479725</v>
+        <v>49.71100417537586</v>
       </c>
       <c r="E19">
-        <v>-10.96</v>
+        <v>-10.14</v>
       </c>
       <c r="F19">
-        <v>13.94</v>
+        <v>14.76</v>
       </c>
       <c r="G19">
         <v>31.9</v>
@@ -2839,28 +2839,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M19">
-        <v>0.7457900000000001</v>
+        <v>0.78966</v>
       </c>
       <c r="N19">
-        <v>5.994209999999999</v>
+        <v>5.950339999999999</v>
       </c>
       <c r="O19">
-        <v>1.798263</v>
+        <v>1.785102</v>
       </c>
       <c r="P19">
-        <v>4.195946999999999</v>
+        <v>4.165238</v>
       </c>
       <c r="Q19">
-        <v>9.055947</v>
+        <v>9.025238</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.06681197258178177</v>
+        <v>0.06700098258984222</v>
       </c>
       <c r="T19">
-        <v>0.4852649556993482</v>
+        <v>0.4896300829062867</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.037396586170367</v>
+        <v>8.535318998049792</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06168180572367062</v>
+        <v>0.06154317420446235</v>
       </c>
       <c r="C20">
-        <v>66.85100417537585</v>
+        <v>66.07121756156623</v>
       </c>
       <c r="D20">
-        <v>49.71100417537586</v>
+        <v>49.75121756156624</v>
       </c>
       <c r="E20">
-        <v>-10.14</v>
+        <v>-9.319999999999999</v>
       </c>
       <c r="F20">
-        <v>14.76</v>
+        <v>15.58</v>
       </c>
       <c r="G20">
         <v>31.9</v>
@@ -2921,28 +2921,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M20">
-        <v>0.7896599999999999</v>
+        <v>0.83353</v>
       </c>
       <c r="N20">
-        <v>5.95034</v>
+        <v>5.90647</v>
       </c>
       <c r="O20">
-        <v>1.785102</v>
+        <v>1.771941</v>
       </c>
       <c r="P20">
-        <v>4.165238</v>
+        <v>4.134529</v>
       </c>
       <c r="Q20">
-        <v>9.025238</v>
+        <v>8.994529</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.06700098258984222</v>
+        <v>0.06719465951168191</v>
       </c>
       <c r="T20">
-        <v>0.4896300829062867</v>
+        <v>0.494102991031915</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.535318998049794</v>
+        <v>8.086091682362962</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06154317420446235</v>
+        <v>0.0614045426852541</v>
       </c>
       <c r="C21">
-        <v>66.07121756156623</v>
+        <v>65.29149606113222</v>
       </c>
       <c r="D21">
-        <v>49.75121756156624</v>
+        <v>49.79149606113223</v>
       </c>
       <c r="E21">
-        <v>-9.319999999999999</v>
+        <v>-8.499999999999996</v>
       </c>
       <c r="F21">
-        <v>15.58</v>
+        <v>16.4</v>
       </c>
       <c r="G21">
         <v>31.9</v>
@@ -3003,28 +3003,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M21">
-        <v>0.83353</v>
+        <v>0.8774000000000001</v>
       </c>
       <c r="N21">
-        <v>5.90647</v>
+        <v>5.8626</v>
       </c>
       <c r="O21">
-        <v>1.771941</v>
+        <v>1.75878</v>
       </c>
       <c r="P21">
-        <v>4.134529</v>
+        <v>4.10382</v>
       </c>
       <c r="Q21">
-        <v>8.994529</v>
+        <v>8.96382</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.06719465951168191</v>
+        <v>0.06739317835656762</v>
       </c>
       <c r="T21">
-        <v>0.494102991031915</v>
+        <v>0.4986877218606842</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.086091682362962</v>
+        <v>7.681787098244813</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0614045426852541</v>
+        <v>0.06138351116604585</v>
       </c>
       <c r="C22">
-        <v>65.29149606113222</v>
+        <v>64.47761233259556</v>
       </c>
       <c r="D22">
-        <v>49.79149606113223</v>
+        <v>49.79761233259556</v>
       </c>
       <c r="E22">
-        <v>-8.499999999999996</v>
+        <v>-7.679999999999996</v>
       </c>
       <c r="F22">
-        <v>16.4</v>
+        <v>17.22</v>
       </c>
       <c r="G22">
         <v>31.9</v>
@@ -3085,45 +3085,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M22">
-        <v>0.8774000000000001</v>
+        <v>0.9350460000000002</v>
       </c>
       <c r="N22">
-        <v>5.8626</v>
+        <v>5.804954</v>
       </c>
       <c r="O22">
-        <v>1.75878</v>
+        <v>1.7414862</v>
       </c>
       <c r="P22">
-        <v>4.10382</v>
+        <v>4.0634678</v>
       </c>
       <c r="Q22">
-        <v>8.96382</v>
+        <v>8.923467800000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.06739317835656762</v>
+        <v>0.06759672299499474</v>
       </c>
       <c r="T22">
-        <v>0.4986877218606842</v>
+        <v>0.5033885218243589</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.681787098244813</v>
+        <v>7.208201521636367</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06138351116604583</v>
+        <v>0.06125047964683759</v>
       </c>
       <c r="C23">
-        <v>64.47761233259556</v>
+        <v>63.69633467105177</v>
       </c>
       <c r="D23">
-        <v>49.79761233259556</v>
+        <v>49.83633467105177</v>
       </c>
       <c r="E23">
-        <v>-7.68</v>
+        <v>-6.859999999999999</v>
       </c>
       <c r="F23">
-        <v>17.22</v>
+        <v>18.04</v>
       </c>
       <c r="G23">
         <v>31.9</v>
@@ -3167,28 +3167,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M23">
-        <v>0.9350459999999999</v>
+        <v>0.979572</v>
       </c>
       <c r="N23">
-        <v>5.804954</v>
+        <v>5.760427999999999</v>
       </c>
       <c r="O23">
-        <v>1.7414862</v>
+        <v>1.7281284</v>
       </c>
       <c r="P23">
-        <v>4.0634678</v>
+        <v>4.0322996</v>
       </c>
       <c r="Q23">
-        <v>8.923467800000001</v>
+        <v>8.892299600000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.06759672299499472</v>
+        <v>0.06780548672671485</v>
       </c>
       <c r="T23">
-        <v>0.5033885218243588</v>
+        <v>0.5082098551204354</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.208201521636369</v>
+        <v>6.880555997925624</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06125047964683759</v>
+        <v>0.06111744812762933</v>
       </c>
       <c r="C24">
-        <v>63.69633467105177</v>
+        <v>62.9151172769093</v>
       </c>
       <c r="D24">
-        <v>49.83633467105177</v>
+        <v>49.87511727690929</v>
       </c>
       <c r="E24">
-        <v>-6.859999999999999</v>
+        <v>-6.039999999999999</v>
       </c>
       <c r="F24">
-        <v>18.04</v>
+        <v>18.86</v>
       </c>
       <c r="G24">
         <v>31.9</v>
@@ -3249,28 +3249,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M24">
-        <v>0.979572</v>
+        <v>1.024098</v>
       </c>
       <c r="N24">
-        <v>5.760427999999999</v>
+        <v>5.715902</v>
       </c>
       <c r="O24">
-        <v>1.7281284</v>
+        <v>1.7147706</v>
       </c>
       <c r="P24">
-        <v>4.0322996</v>
+        <v>4.0011314</v>
       </c>
       <c r="Q24">
-        <v>8.892299600000001</v>
+        <v>8.861131400000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.06780548672671485</v>
+        <v>0.0680196728930251</v>
       </c>
       <c r="T24">
-        <v>0.5082098551204354</v>
+        <v>0.5131564178527737</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.880555997925624</v>
+        <v>6.581401389320162</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06111744812762933</v>
+        <v>0.06098441660842106</v>
       </c>
       <c r="C25">
-        <v>62.9151172769093</v>
+        <v>62.13396029097784</v>
       </c>
       <c r="D25">
-        <v>49.87511727690929</v>
+        <v>49.91396029097785</v>
       </c>
       <c r="E25">
-        <v>-6.039999999999999</v>
+        <v>-5.219999999999995</v>
       </c>
       <c r="F25">
-        <v>18.86</v>
+        <v>19.68</v>
       </c>
       <c r="G25">
         <v>31.9</v>
@@ -3331,28 +3331,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M25">
-        <v>1.024098</v>
+        <v>1.068624</v>
       </c>
       <c r="N25">
-        <v>5.715902</v>
+        <v>5.671375999999999</v>
       </c>
       <c r="O25">
-        <v>1.7147706</v>
+        <v>1.7014128</v>
       </c>
       <c r="P25">
-        <v>4.0011314</v>
+        <v>3.969963199999999</v>
       </c>
       <c r="Q25">
-        <v>8.861131400000001</v>
+        <v>8.8299632</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0680196728930251</v>
+        <v>0.06823949553739614</v>
       </c>
       <c r="T25">
-        <v>0.5131564178527737</v>
+        <v>0.5182331532885945</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.581401389320162</v>
+        <v>6.30717633143182</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06098441660842106</v>
+        <v>0.06102638508921281</v>
       </c>
       <c r="C26">
-        <v>62.13396029097785</v>
+        <v>61.30169965416002</v>
       </c>
       <c r="D26">
-        <v>49.91396029097785</v>
+        <v>49.90169965416003</v>
       </c>
       <c r="E26">
-        <v>-5.219999999999999</v>
+        <v>-4.399999999999999</v>
       </c>
       <c r="F26">
-        <v>19.68</v>
+        <v>20.5</v>
       </c>
       <c r="G26">
         <v>31.9</v>
@@ -3413,45 +3413,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M26">
-        <v>1.068624</v>
+        <v>1.13365</v>
       </c>
       <c r="N26">
-        <v>5.671376</v>
+        <v>5.606349999999999</v>
       </c>
       <c r="O26">
-        <v>1.7014128</v>
+        <v>1.681905</v>
       </c>
       <c r="P26">
-        <v>3.9699632</v>
+        <v>3.924445</v>
       </c>
       <c r="Q26">
-        <v>8.8299632</v>
+        <v>8.784445</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.06823949553739614</v>
+        <v>0.06846518011895042</v>
       </c>
       <c r="T26">
-        <v>0.5182331532885945</v>
+        <v>0.5234452683360373</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.307176331431822</v>
+        <v>5.945397609491464</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06102638508921281</v>
+        <v>0.06090035357000455</v>
       </c>
       <c r="C27">
-        <v>61.30169965416002</v>
+        <v>60.51853652510999</v>
       </c>
       <c r="D27">
-        <v>49.90169965416003</v>
+        <v>49.93853652511</v>
       </c>
       <c r="E27">
-        <v>-4.399999999999999</v>
+        <v>-3.579999999999998</v>
       </c>
       <c r="F27">
-        <v>20.5</v>
+        <v>21.32</v>
       </c>
       <c r="G27">
         <v>31.9</v>
@@ -3495,28 +3495,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M27">
-        <v>1.13365</v>
+        <v>1.178996</v>
       </c>
       <c r="N27">
-        <v>5.606349999999999</v>
+        <v>5.561003999999999</v>
       </c>
       <c r="O27">
-        <v>1.681905</v>
+        <v>1.668301199999999</v>
       </c>
       <c r="P27">
-        <v>3.924445</v>
+        <v>3.892702799999999</v>
       </c>
       <c r="Q27">
-        <v>8.784445</v>
+        <v>8.7527028</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.06846518011895042</v>
+        <v>0.06869696428378994</v>
       </c>
       <c r="T27">
-        <v>0.5234452683360373</v>
+        <v>0.5287982513577353</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.945397609491464</v>
+        <v>5.716728470664869</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06090035357000455</v>
+        <v>0.06077432205079629</v>
       </c>
       <c r="C28">
-        <v>60.51853652510999</v>
+        <v>59.73542782136009</v>
       </c>
       <c r="D28">
-        <v>49.93853652511</v>
+        <v>49.97542782136009</v>
       </c>
       <c r="E28">
-        <v>-3.579999999999998</v>
+        <v>-2.759999999999998</v>
       </c>
       <c r="F28">
-        <v>21.32</v>
+        <v>22.14</v>
       </c>
       <c r="G28">
         <v>31.9</v>
@@ -3577,28 +3577,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M28">
-        <v>1.178996</v>
+        <v>1.224342</v>
       </c>
       <c r="N28">
-        <v>5.561003999999999</v>
+        <v>5.515657999999999</v>
       </c>
       <c r="O28">
-        <v>1.668301199999999</v>
+        <v>1.6546974</v>
       </c>
       <c r="P28">
-        <v>3.892702799999999</v>
+        <v>3.860960599999999</v>
       </c>
       <c r="Q28">
-        <v>8.7527028</v>
+        <v>8.7209606</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.06869696428378994</v>
+        <v>0.06893509869972095</v>
       </c>
       <c r="T28">
-        <v>0.5287982513577353</v>
+        <v>0.5342978914485209</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.716728470664869</v>
+        <v>5.504997786566171</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06077432205079629</v>
+        <v>0.06064829053158804</v>
       </c>
       <c r="C29">
-        <v>59.73542782136009</v>
+        <v>58.95237366361693</v>
       </c>
       <c r="D29">
-        <v>49.97542782136009</v>
+        <v>50.01237366361694</v>
       </c>
       <c r="E29">
-        <v>-2.759999999999998</v>
+        <v>-1.939999999999998</v>
       </c>
       <c r="F29">
-        <v>22.14</v>
+        <v>22.96</v>
       </c>
       <c r="G29">
         <v>31.9</v>
@@ -3659,28 +3659,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M29">
-        <v>1.224342</v>
+        <v>1.269688</v>
       </c>
       <c r="N29">
-        <v>5.515657999999999</v>
+        <v>5.470311999999999</v>
       </c>
       <c r="O29">
-        <v>1.6546974</v>
+        <v>1.6410936</v>
       </c>
       <c r="P29">
-        <v>3.860960599999999</v>
+        <v>3.829218399999999</v>
       </c>
       <c r="Q29">
-        <v>8.7209606</v>
+        <v>8.6892184</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.06893509869972095</v>
+        <v>0.06917984796053894</v>
       </c>
       <c r="T29">
-        <v>0.5342978914485209</v>
+        <v>0.539950299319606</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.504997786566171</v>
+        <v>5.308390722760236</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06064829053158804</v>
+        <v>0.06052225901237977</v>
       </c>
       <c r="C30">
-        <v>58.95237366361693</v>
+        <v>58.1693741729444</v>
       </c>
       <c r="D30">
-        <v>50.01237366361694</v>
+        <v>50.0493741729444</v>
       </c>
       <c r="E30">
-        <v>-1.939999999999998</v>
+        <v>-1.119999999999997</v>
       </c>
       <c r="F30">
-        <v>22.96</v>
+        <v>23.78</v>
       </c>
       <c r="G30">
         <v>31.9</v>
@@ -3741,28 +3741,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M30">
-        <v>1.269688</v>
+        <v>1.315034</v>
       </c>
       <c r="N30">
-        <v>5.470311999999999</v>
+        <v>5.424966</v>
       </c>
       <c r="O30">
-        <v>1.6410936</v>
+        <v>1.6274898</v>
       </c>
       <c r="P30">
-        <v>3.829218399999999</v>
+        <v>3.7974762</v>
       </c>
       <c r="Q30">
-        <v>8.6892184</v>
+        <v>8.6574762</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.06917984796053894</v>
+        <v>0.06943149156673208</v>
       </c>
       <c r="T30">
-        <v>0.539950299319606</v>
+        <v>0.5457619299476232</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.308390722760236</v>
+        <v>5.125342766802987</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06052225901237977</v>
+        <v>0.06039622749317151</v>
       </c>
       <c r="C31">
-        <v>58.1693741729444</v>
+        <v>57.38642947076484</v>
       </c>
       <c r="D31">
-        <v>50.0493741729444</v>
+        <v>50.08642947076483</v>
       </c>
       <c r="E31">
-        <v>-1.120000000000001</v>
+        <v>-0.3000000000000007</v>
       </c>
       <c r="F31">
-        <v>23.78</v>
+        <v>24.6</v>
       </c>
       <c r="G31">
         <v>31.9</v>
@@ -3823,28 +3823,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M31">
-        <v>1.315034</v>
+        <v>1.36038</v>
       </c>
       <c r="N31">
-        <v>5.424966</v>
+        <v>5.379619999999999</v>
       </c>
       <c r="O31">
-        <v>1.6274898</v>
+        <v>1.613886</v>
       </c>
       <c r="P31">
-        <v>3.7974762</v>
+        <v>3.765733999999999</v>
       </c>
       <c r="Q31">
-        <v>8.6574762</v>
+        <v>8.625734</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.06943149156673208</v>
+        <v>0.06969032499024502</v>
       </c>
       <c r="T31">
-        <v>0.5457619299476232</v>
+        <v>0.5517396071650124</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.125342766802988</v>
+        <v>4.954498007909555</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06039622749317151</v>
+        <v>0.06027019597396326</v>
       </c>
       <c r="C32">
-        <v>57.38642947076484</v>
+        <v>56.60353967886046</v>
       </c>
       <c r="D32">
-        <v>50.08642947076483</v>
+        <v>50.12353967886046</v>
       </c>
       <c r="E32">
-        <v>-0.3000000000000007</v>
+        <v>0.5199999999999996</v>
       </c>
       <c r="F32">
-        <v>24.6</v>
+        <v>25.42</v>
       </c>
       <c r="G32">
         <v>31.9</v>
@@ -3905,28 +3905,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M32">
-        <v>1.36038</v>
+        <v>1.405726</v>
       </c>
       <c r="N32">
-        <v>5.379619999999999</v>
+        <v>5.334273999999999</v>
       </c>
       <c r="O32">
-        <v>1.613886</v>
+        <v>1.6002822</v>
       </c>
       <c r="P32">
-        <v>3.765733999999999</v>
+        <v>3.733991799999999</v>
       </c>
       <c r="Q32">
-        <v>8.625734</v>
+        <v>8.5939918</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.06969032499024502</v>
+        <v>0.06995666083183082</v>
       </c>
       <c r="T32">
-        <v>0.5517396071650124</v>
+        <v>0.5578905503887025</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.954498007909555</v>
+        <v>4.794675491525375</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06027019597396326</v>
+        <v>0.060144164454755</v>
       </c>
       <c r="C33">
-        <v>56.60353967886046</v>
+        <v>55.82070491937473</v>
       </c>
       <c r="D33">
-        <v>50.12353967886046</v>
+        <v>50.16070491937474</v>
       </c>
       <c r="E33">
-        <v>0.5199999999999996</v>
+        <v>1.340000000000003</v>
       </c>
       <c r="F33">
-        <v>25.42</v>
+        <v>26.24</v>
       </c>
       <c r="G33">
         <v>31.9</v>
@@ -3987,28 +3987,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M33">
-        <v>1.405726</v>
+        <v>1.451072</v>
       </c>
       <c r="N33">
-        <v>5.334273999999999</v>
+        <v>5.288927999999999</v>
       </c>
       <c r="O33">
-        <v>1.6002822</v>
+        <v>1.5866784</v>
       </c>
       <c r="P33">
-        <v>3.733991799999999</v>
+        <v>3.7022496</v>
       </c>
       <c r="Q33">
-        <v>8.5939918</v>
+        <v>8.562249599999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.06995666083183082</v>
+        <v>0.07023083008052206</v>
       </c>
       <c r="T33">
-        <v>0.5578905503887025</v>
+        <v>0.5642224037072071</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.794675491525375</v>
+        <v>4.644841882415207</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.060144164454755</v>
+        <v>0.06001813293554675</v>
       </c>
       <c r="C34">
-        <v>55.82070491937473</v>
+        <v>55.03792531481358</v>
       </c>
       <c r="D34">
-        <v>50.16070491937474</v>
+        <v>50.19792531481359</v>
       </c>
       <c r="E34">
-        <v>1.340000000000003</v>
+        <v>2.160000000000004</v>
       </c>
       <c r="F34">
-        <v>26.24</v>
+        <v>27.06</v>
       </c>
       <c r="G34">
         <v>31.9</v>
@@ -4069,28 +4069,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M34">
-        <v>1.451072</v>
+        <v>1.496418</v>
       </c>
       <c r="N34">
-        <v>5.288927999999999</v>
+        <v>5.243581999999999</v>
       </c>
       <c r="O34">
-        <v>1.5866784</v>
+        <v>1.5730746</v>
       </c>
       <c r="P34">
-        <v>3.7022496</v>
+        <v>3.670507399999999</v>
       </c>
       <c r="Q34">
-        <v>8.562249599999999</v>
+        <v>8.530507399999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07023083008052206</v>
+        <v>0.07051318348589067</v>
       </c>
       <c r="T34">
-        <v>0.5642224037072071</v>
+        <v>0.5707432675725329</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.644841882415207</v>
+        <v>4.504089098099594</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06001813293554675</v>
+        <v>0.06048710141633849</v>
       </c>
       <c r="C35">
-        <v>55.03792531481358</v>
+        <v>54.07970555747949</v>
       </c>
       <c r="D35">
-        <v>50.19792531481359</v>
+        <v>50.0597055574795</v>
       </c>
       <c r="E35">
-        <v>2.160000000000004</v>
+        <v>2.980000000000004</v>
       </c>
       <c r="F35">
-        <v>27.06</v>
+        <v>27.88</v>
       </c>
       <c r="G35">
         <v>31.9</v>
@@ -4151,45 +4151,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M35">
-        <v>1.496418</v>
+        <v>1.611464</v>
       </c>
       <c r="N35">
-        <v>5.243581999999999</v>
+        <v>5.128535999999999</v>
       </c>
       <c r="O35">
-        <v>1.5730746</v>
+        <v>1.5385608</v>
       </c>
       <c r="P35">
-        <v>3.670507399999999</v>
+        <v>3.589975199999999</v>
       </c>
       <c r="Q35">
-        <v>8.530507399999999</v>
+        <v>8.449975199999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07051318348589067</v>
+        <v>0.07080409305505832</v>
       </c>
       <c r="T35">
-        <v>0.5707432675725329</v>
+        <v>0.5774617333731714</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.504089098099594</v>
+        <v>4.182532157094418</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06048710141633849</v>
+        <v>0.06037856989713022</v>
       </c>
       <c r="C36">
-        <v>54.07970555747949</v>
+        <v>53.29162547130169</v>
       </c>
       <c r="D36">
-        <v>50.0597055574795</v>
+        <v>50.09162547130168</v>
       </c>
       <c r="E36">
-        <v>2.980000000000004</v>
+        <v>3.800000000000004</v>
       </c>
       <c r="F36">
-        <v>27.88</v>
+        <v>28.7</v>
       </c>
       <c r="G36">
         <v>31.9</v>
@@ -4233,28 +4233,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M36">
-        <v>1.611464</v>
+        <v>1.65886</v>
       </c>
       <c r="N36">
-        <v>5.128535999999999</v>
+        <v>5.08114</v>
       </c>
       <c r="O36">
-        <v>1.5385608</v>
+        <v>1.524342</v>
       </c>
       <c r="P36">
-        <v>3.589975199999999</v>
+        <v>3.556798</v>
       </c>
       <c r="Q36">
-        <v>8.449975199999999</v>
+        <v>8.416798</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07080409305505832</v>
+        <v>0.07110395368789266</v>
       </c>
       <c r="T36">
-        <v>0.5774617333731714</v>
+        <v>0.5843869211984449</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.182532157094418</v>
+        <v>4.063031238320292</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06037856989713022</v>
+        <v>0.06115203837792196</v>
       </c>
       <c r="C37">
-        <v>53.29162547130169</v>
+        <v>52.24502739440968</v>
       </c>
       <c r="D37">
-        <v>50.09162547130168</v>
+        <v>49.86502739440968</v>
       </c>
       <c r="E37">
-        <v>3.800000000000004</v>
+        <v>4.620000000000005</v>
       </c>
       <c r="F37">
-        <v>28.7</v>
+        <v>29.52</v>
       </c>
       <c r="G37">
         <v>31.9</v>
@@ -4315,45 +4315,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M37">
-        <v>1.65886</v>
+        <v>1.809576</v>
       </c>
       <c r="N37">
-        <v>5.08114</v>
+        <v>4.930423999999999</v>
       </c>
       <c r="O37">
-        <v>1.524342</v>
+        <v>1.4791272</v>
       </c>
       <c r="P37">
-        <v>3.556798</v>
+        <v>3.451296799999999</v>
       </c>
       <c r="Q37">
-        <v>8.416798</v>
+        <v>8.311296799999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07110395368789266</v>
+        <v>0.07141318496550308</v>
       </c>
       <c r="T37">
-        <v>0.5843869211984449</v>
+        <v>0.5915285211432584</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.063031238320292</v>
+        <v>3.724629415951581</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06115203837792198</v>
+        <v>0.06106800685871371</v>
       </c>
       <c r="C38">
-        <v>52.24502739440969</v>
+        <v>51.4495462526987</v>
       </c>
       <c r="D38">
-        <v>49.86502739440968</v>
+        <v>49.88954625269869</v>
       </c>
       <c r="E38">
-        <v>4.620000000000001</v>
+        <v>5.440000000000001</v>
       </c>
       <c r="F38">
-        <v>29.52</v>
+        <v>30.34</v>
       </c>
       <c r="G38">
         <v>31.9</v>
@@ -4397,28 +4397,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M38">
-        <v>1.809576</v>
+        <v>1.859842</v>
       </c>
       <c r="N38">
-        <v>4.930423999999999</v>
+        <v>4.880158</v>
       </c>
       <c r="O38">
-        <v>1.4791272</v>
+        <v>1.4640474</v>
       </c>
       <c r="P38">
-        <v>3.4512968</v>
+        <v>3.4161106</v>
       </c>
       <c r="Q38">
-        <v>8.311296800000001</v>
+        <v>8.276110599999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07141318496550308</v>
+        <v>0.07173223310906938</v>
       </c>
       <c r="T38">
-        <v>0.5915285211432584</v>
+        <v>0.5988968385466372</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.724629415951582</v>
+        <v>3.623963756060999</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06106800685871371</v>
+        <v>0.06098397533950546</v>
       </c>
       <c r="C39">
-        <v>51.4495462526987</v>
+        <v>50.65408923491538</v>
       </c>
       <c r="D39">
-        <v>49.88954625269869</v>
+        <v>49.91408923491538</v>
       </c>
       <c r="E39">
-        <v>5.440000000000001</v>
+        <v>6.260000000000002</v>
       </c>
       <c r="F39">
-        <v>30.34</v>
+        <v>31.16</v>
       </c>
       <c r="G39">
         <v>31.9</v>
@@ -4479,28 +4479,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M39">
-        <v>1.859842</v>
+        <v>1.910108</v>
       </c>
       <c r="N39">
-        <v>4.880158</v>
+        <v>4.829891999999999</v>
       </c>
       <c r="O39">
-        <v>1.4640474</v>
+        <v>1.4489676</v>
       </c>
       <c r="P39">
-        <v>3.4161106</v>
+        <v>3.3809244</v>
       </c>
       <c r="Q39">
-        <v>8.276110599999999</v>
+        <v>8.240924400000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07173223310906938</v>
+        <v>0.07206157312823461</v>
       </c>
       <c r="T39">
-        <v>0.5988968385466372</v>
+        <v>0.6065028436081896</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.623963756060999</v>
+        <v>3.528596288796235</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06098397533950546</v>
+        <v>0.0616643438202972</v>
       </c>
       <c r="C40">
-        <v>50.65408923491538</v>
+        <v>49.63606583903631</v>
       </c>
       <c r="D40">
-        <v>49.91408923491538</v>
+        <v>49.7160658390363</v>
       </c>
       <c r="E40">
-        <v>6.260000000000002</v>
+        <v>7.080000000000002</v>
       </c>
       <c r="F40">
-        <v>31.16</v>
+        <v>31.98</v>
       </c>
       <c r="G40">
         <v>31.9</v>
@@ -4561,45 +4561,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M40">
-        <v>1.910108</v>
+        <v>2.049918</v>
       </c>
       <c r="N40">
-        <v>4.829891999999999</v>
+        <v>4.690081999999999</v>
       </c>
       <c r="O40">
-        <v>1.4489676</v>
+        <v>1.4070246</v>
       </c>
       <c r="P40">
-        <v>3.3809244</v>
+        <v>3.283057399999999</v>
       </c>
       <c r="Q40">
-        <v>8.240924400000001</v>
+        <v>8.1430574</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07206157312823461</v>
+        <v>0.07240171118081508</v>
       </c>
       <c r="T40">
-        <v>0.6065028436081896</v>
+        <v>0.614358225884875</v>
       </c>
       <c r="U40">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.528596288796235</v>
+        <v>3.287936395504599</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0616643438202972</v>
+        <v>0.06159991230108894</v>
       </c>
       <c r="C41">
-        <v>49.63606583903631</v>
+        <v>48.83475145807883</v>
       </c>
       <c r="D41">
-        <v>49.7160658390363</v>
+        <v>49.73475145807884</v>
       </c>
       <c r="E41">
-        <v>7.080000000000002</v>
+        <v>7.900000000000006</v>
       </c>
       <c r="F41">
-        <v>31.98</v>
+        <v>32.8</v>
       </c>
       <c r="G41">
         <v>31.9</v>
@@ -4643,28 +4643,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M41">
-        <v>2.049918</v>
+        <v>2.10248</v>
       </c>
       <c r="N41">
-        <v>4.690081999999999</v>
+        <v>4.637519999999999</v>
       </c>
       <c r="O41">
-        <v>1.4070246</v>
+        <v>1.391256</v>
       </c>
       <c r="P41">
-        <v>3.283057399999999</v>
+        <v>3.246263999999999</v>
       </c>
       <c r="Q41">
-        <v>8.1430574</v>
+        <v>8.106263999999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07240171118081508</v>
+        <v>0.07275318716848157</v>
       </c>
       <c r="T41">
-        <v>0.614358225884875</v>
+        <v>0.6224754542374498</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.287936395504599</v>
+        <v>3.205737985616985</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06159991230108894</v>
+        <v>0.06153548078188068</v>
       </c>
       <c r="C42">
-        <v>48.83475145807883</v>
+        <v>48.03345112825878</v>
       </c>
       <c r="D42">
-        <v>49.73475145807884</v>
+        <v>49.75345112825878</v>
       </c>
       <c r="E42">
-        <v>7.900000000000006</v>
+        <v>8.720000000000006</v>
       </c>
       <c r="F42">
-        <v>32.8</v>
+        <v>33.62</v>
       </c>
       <c r="G42">
         <v>31.9</v>
@@ -4725,28 +4725,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M42">
-        <v>2.10248</v>
+        <v>2.155042</v>
       </c>
       <c r="N42">
-        <v>4.637519999999999</v>
+        <v>4.584957999999999</v>
       </c>
       <c r="O42">
-        <v>1.391256</v>
+        <v>1.375487399999999</v>
       </c>
       <c r="P42">
-        <v>3.246263999999999</v>
+        <v>3.209470599999999</v>
       </c>
       <c r="Q42">
-        <v>8.106263999999999</v>
+        <v>8.069470599999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.07275318716848157</v>
+        <v>0.07311657759640794</v>
       </c>
       <c r="T42">
-        <v>0.6224754542374498</v>
+        <v>0.6308678428731627</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.205737985616985</v>
+        <v>3.127549254260473</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06153548078188068</v>
+        <v>0.06147104926267243</v>
       </c>
       <c r="C43">
-        <v>48.03345112825878</v>
+        <v>47.23216486543125</v>
       </c>
       <c r="D43">
-        <v>49.75345112825878</v>
+        <v>49.77216486543126</v>
       </c>
       <c r="E43">
-        <v>8.720000000000006</v>
+        <v>9.540000000000006</v>
       </c>
       <c r="F43">
-        <v>33.62</v>
+        <v>34.44</v>
       </c>
       <c r="G43">
         <v>31.9</v>
@@ -4807,28 +4807,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M43">
-        <v>2.155042</v>
+        <v>2.207604</v>
       </c>
       <c r="N43">
-        <v>4.584957999999999</v>
+        <v>4.532395999999999</v>
       </c>
       <c r="O43">
-        <v>1.375487399999999</v>
+        <v>1.3597188</v>
       </c>
       <c r="P43">
-        <v>3.209470599999999</v>
+        <v>3.172677199999999</v>
       </c>
       <c r="Q43">
-        <v>8.069470599999999</v>
+        <v>8.032677199999998</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.07311657759640794</v>
+        <v>0.07349249872874557</v>
       </c>
       <c r="T43">
-        <v>0.6308678428731627</v>
+        <v>0.6395496242204519</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.127549254260473</v>
+        <v>3.0530837958257</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06147104926267243</v>
+        <v>0.06375441774346416</v>
       </c>
       <c r="C44">
-        <v>47.23216486543126</v>
+        <v>45.75745214954338</v>
       </c>
       <c r="D44">
-        <v>49.77216486543126</v>
+        <v>49.11745214954338</v>
       </c>
       <c r="E44">
-        <v>9.539999999999999</v>
+        <v>10.36</v>
       </c>
       <c r="F44">
-        <v>34.44</v>
+        <v>35.26</v>
       </c>
       <c r="G44">
         <v>31.9</v>
@@ -4889,45 +4889,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M44">
-        <v>2.207604</v>
+        <v>2.535194</v>
       </c>
       <c r="N44">
-        <v>4.532395999999999</v>
+        <v>4.204806</v>
       </c>
       <c r="O44">
-        <v>1.3597188</v>
+        <v>1.2614418</v>
       </c>
       <c r="P44">
-        <v>3.1726772</v>
+        <v>2.9433642</v>
       </c>
       <c r="Q44">
-        <v>8.0326772</v>
+        <v>7.8033642</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.07349249872874555</v>
+        <v>0.07388161007625292</v>
       </c>
       <c r="T44">
-        <v>0.6395496242204518</v>
+        <v>0.6485360294746635</v>
       </c>
       <c r="U44">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.0530837958257</v>
+        <v>2.658573663396174</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06375441774346416</v>
+        <v>0.06374458622425591</v>
       </c>
       <c r="C45">
-        <v>45.75745214954338</v>
+        <v>44.94023422755744</v>
       </c>
       <c r="D45">
-        <v>49.11745214954338</v>
+        <v>49.12023422755745</v>
       </c>
       <c r="E45">
-        <v>10.36</v>
+        <v>11.18</v>
       </c>
       <c r="F45">
-        <v>35.26</v>
+        <v>36.08</v>
       </c>
       <c r="G45">
         <v>31.9</v>
@@ -4971,28 +4971,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M45">
-        <v>2.535194</v>
+        <v>2.594152</v>
       </c>
       <c r="N45">
-        <v>4.204806</v>
+        <v>4.145847999999999</v>
       </c>
       <c r="O45">
-        <v>1.2614418</v>
+        <v>1.2437544</v>
       </c>
       <c r="P45">
-        <v>2.9433642</v>
+        <v>2.9020936</v>
       </c>
       <c r="Q45">
-        <v>7.8033642</v>
+        <v>7.7620936</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.07388161007625292</v>
+        <v>0.07428461825759984</v>
       </c>
       <c r="T45">
-        <v>0.6485360294746635</v>
+        <v>0.6578433777736684</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.658573663396174</v>
+        <v>2.598151534682624</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06374458622425591</v>
+        <v>0.06373475470504765</v>
       </c>
       <c r="C46">
-        <v>44.94023422755744</v>
+        <v>44.12301662075061</v>
       </c>
       <c r="D46">
-        <v>49.12023422755745</v>
+        <v>49.1230166207506</v>
       </c>
       <c r="E46">
-        <v>11.18</v>
+        <v>12</v>
       </c>
       <c r="F46">
-        <v>36.08</v>
+        <v>36.9</v>
       </c>
       <c r="G46">
         <v>31.9</v>
@@ -5053,28 +5053,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M46">
-        <v>2.594152</v>
+        <v>2.65311</v>
       </c>
       <c r="N46">
-        <v>4.145847999999999</v>
+        <v>4.086889999999999</v>
       </c>
       <c r="O46">
-        <v>1.2437544</v>
+        <v>1.226067</v>
       </c>
       <c r="P46">
-        <v>2.9020936</v>
+        <v>2.860822999999999</v>
       </c>
       <c r="Q46">
-        <v>7.7620936</v>
+        <v>7.720822999999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.07428461825759984</v>
+        <v>0.07470228128190481</v>
       </c>
       <c r="T46">
-        <v>0.6578433777736684</v>
+        <v>0.6674891751017281</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.598151534682624</v>
+        <v>2.540414833911899</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06373475470504765</v>
+        <v>0.06498072318583939</v>
       </c>
       <c r="C47">
-        <v>44.12301662075061</v>
+        <v>42.95289171682737</v>
       </c>
       <c r="D47">
-        <v>49.1230166207506</v>
+        <v>48.77289171682737</v>
       </c>
       <c r="E47">
-        <v>12</v>
+        <v>12.82</v>
       </c>
       <c r="F47">
-        <v>36.9</v>
+        <v>37.72</v>
       </c>
       <c r="G47">
         <v>31.9</v>
@@ -5135,45 +5135,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M47">
-        <v>2.65311</v>
+        <v>2.859176</v>
       </c>
       <c r="N47">
-        <v>4.086889999999999</v>
+        <v>3.880823999999999</v>
       </c>
       <c r="O47">
-        <v>1.226067</v>
+        <v>1.1642472</v>
       </c>
       <c r="P47">
-        <v>2.860822999999999</v>
+        <v>2.716576799999999</v>
       </c>
       <c r="Q47">
-        <v>7.720822999999999</v>
+        <v>7.5765768</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.07470228128190481</v>
+        <v>0.07513541330710999</v>
       </c>
       <c r="T47">
-        <v>0.6674891751017281</v>
+        <v>0.6774922241826788</v>
       </c>
       <c r="U47">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.540414833911899</v>
+        <v>2.357322529288158</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06498072318583939</v>
+        <v>0.06499819166663114</v>
       </c>
       <c r="C48">
-        <v>42.95289171682737</v>
+        <v>42.12801843908327</v>
       </c>
       <c r="D48">
-        <v>48.77289171682737</v>
+        <v>48.76801843908327</v>
       </c>
       <c r="E48">
-        <v>12.82</v>
+        <v>13.64</v>
       </c>
       <c r="F48">
-        <v>37.72</v>
+        <v>38.54</v>
       </c>
       <c r="G48">
         <v>31.9</v>
@@ -5217,28 +5217,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M48">
-        <v>2.859176</v>
+        <v>2.921332</v>
       </c>
       <c r="N48">
-        <v>3.880823999999999</v>
+        <v>3.818667999999999</v>
       </c>
       <c r="O48">
-        <v>1.1642472</v>
+        <v>1.1456004</v>
       </c>
       <c r="P48">
-        <v>2.716576799999999</v>
+        <v>2.6730676</v>
       </c>
       <c r="Q48">
-        <v>7.5765768</v>
+        <v>7.5330676</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.07513541330710999</v>
+        <v>0.07558488993703988</v>
       </c>
       <c r="T48">
-        <v>0.6774922241826788</v>
+        <v>0.6878727468138542</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.357322529288158</v>
+        <v>2.307166730792666</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06499819166663114</v>
+        <v>0.06501566014742288</v>
       </c>
       <c r="C49">
-        <v>42.12801843908327</v>
+        <v>41.30314613509579</v>
       </c>
       <c r="D49">
-        <v>48.76801843908327</v>
+        <v>48.7631461350958</v>
       </c>
       <c r="E49">
-        <v>13.64</v>
+        <v>14.46000000000001</v>
       </c>
       <c r="F49">
-        <v>38.54</v>
+        <v>39.36000000000001</v>
       </c>
       <c r="G49">
         <v>31.9</v>
@@ -5299,28 +5299,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M49">
-        <v>2.921332</v>
+        <v>2.983488000000001</v>
       </c>
       <c r="N49">
-        <v>3.818667999999999</v>
+        <v>3.756511999999999</v>
       </c>
       <c r="O49">
-        <v>1.1456004</v>
+        <v>1.1269536</v>
       </c>
       <c r="P49">
-        <v>2.6730676</v>
+        <v>2.629558399999999</v>
       </c>
       <c r="Q49">
-        <v>7.5330676</v>
+        <v>7.489558399999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.07558488993703988</v>
+        <v>0.07605165412965939</v>
       </c>
       <c r="T49">
-        <v>0.6878727468138542</v>
+        <v>0.6986525203154593</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.307166730792666</v>
+        <v>2.259100757234484</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06501566014742288</v>
+        <v>0.06503312862821461</v>
       </c>
       <c r="C50">
-        <v>41.3031461350958</v>
+        <v>40.47827480457313</v>
       </c>
       <c r="D50">
-        <v>48.7631461350958</v>
+        <v>48.75827480457313</v>
       </c>
       <c r="E50">
-        <v>14.46</v>
+        <v>15.28</v>
       </c>
       <c r="F50">
-        <v>39.36</v>
+        <v>40.18</v>
       </c>
       <c r="G50">
         <v>31.9</v>
@@ -5381,28 +5381,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M50">
-        <v>2.983488</v>
+        <v>3.045644</v>
       </c>
       <c r="N50">
-        <v>3.756511999999999</v>
+        <v>3.694355999999999</v>
       </c>
       <c r="O50">
-        <v>1.1269536</v>
+        <v>1.1083068</v>
       </c>
       <c r="P50">
-        <v>2.6295584</v>
+        <v>2.5860492</v>
       </c>
       <c r="Q50">
-        <v>7.4895584</v>
+        <v>7.4460492</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.07605165412965939</v>
+        <v>0.07653672280042081</v>
       </c>
       <c r="T50">
-        <v>0.6986525203154593</v>
+        <v>0.7098550300328136</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.259100757234485</v>
+        <v>2.212996660148067</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06503312862821461</v>
+        <v>0.06505059710900636</v>
       </c>
       <c r="C51">
-        <v>40.47827480457313</v>
+        <v>39.65340444722355</v>
       </c>
       <c r="D51">
-        <v>48.75827480457313</v>
+        <v>48.75340444722355</v>
       </c>
       <c r="E51">
-        <v>15.28</v>
+        <v>16.1</v>
       </c>
       <c r="F51">
-        <v>40.18</v>
+        <v>41</v>
       </c>
       <c r="G51">
         <v>31.9</v>
@@ -5463,28 +5463,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M51">
-        <v>3.045644</v>
+        <v>3.1078</v>
       </c>
       <c r="N51">
-        <v>3.694355999999999</v>
+        <v>3.632199999999999</v>
       </c>
       <c r="O51">
-        <v>1.1083068</v>
+        <v>1.08966</v>
       </c>
       <c r="P51">
-        <v>2.5860492</v>
+        <v>2.54254</v>
       </c>
       <c r="Q51">
-        <v>7.4460492</v>
+        <v>7.40254</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.07653672280042081</v>
+        <v>0.07704119421801273</v>
       </c>
       <c r="T51">
-        <v>0.7098550300328136</v>
+        <v>0.7215056401388622</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.212996660148067</v>
+        <v>2.168736726945106</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06505059710900636</v>
+        <v>0.06506806558979811</v>
       </c>
       <c r="C52">
-        <v>39.65340444722355</v>
+        <v>38.82853506275546</v>
       </c>
       <c r="D52">
-        <v>48.75340444722355</v>
+        <v>48.74853506275545</v>
       </c>
       <c r="E52">
-        <v>16.1</v>
+        <v>16.92</v>
       </c>
       <c r="F52">
-        <v>41</v>
+        <v>41.82</v>
       </c>
       <c r="G52">
         <v>31.9</v>
@@ -5545,28 +5545,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M52">
-        <v>3.1078</v>
+        <v>3.169956</v>
       </c>
       <c r="N52">
-        <v>3.632199999999999</v>
+        <v>3.570043999999999</v>
       </c>
       <c r="O52">
-        <v>1.08966</v>
+        <v>1.0710132</v>
       </c>
       <c r="P52">
-        <v>2.54254</v>
+        <v>2.499030799999999</v>
       </c>
       <c r="Q52">
-        <v>7.40254</v>
+        <v>7.359030799999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.07704119421801273</v>
+        <v>0.07756625630571043</v>
       </c>
       <c r="T52">
-        <v>0.7215056401388622</v>
+        <v>0.7336317853512802</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.168736726945106</v>
+        <v>2.126212477397162</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06506806558979811</v>
+        <v>0.06508553407058984</v>
       </c>
       <c r="C53">
-        <v>38.82853506275546</v>
+        <v>38.00366665087738</v>
       </c>
       <c r="D53">
-        <v>48.74853506275545</v>
+        <v>48.74366665087737</v>
       </c>
       <c r="E53">
-        <v>16.92</v>
+        <v>17.74</v>
       </c>
       <c r="F53">
-        <v>41.82</v>
+        <v>42.64</v>
       </c>
       <c r="G53">
         <v>31.9</v>
@@ -5627,28 +5627,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M53">
-        <v>3.169956</v>
+        <v>3.232112</v>
       </c>
       <c r="N53">
-        <v>3.570043999999999</v>
+        <v>3.507887999999999</v>
       </c>
       <c r="O53">
-        <v>1.0710132</v>
+        <v>1.0523664</v>
       </c>
       <c r="P53">
-        <v>2.499030799999999</v>
+        <v>2.455521599999999</v>
       </c>
       <c r="Q53">
-        <v>7.359030799999999</v>
+        <v>7.315521599999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.07756625630571043</v>
+        <v>0.07811319598039551</v>
       </c>
       <c r="T53">
-        <v>0.7336317853512802</v>
+        <v>0.7462631866142153</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.126212477397162</v>
+        <v>2.085323775908755</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06508553407058984</v>
+        <v>0.0651030025513816</v>
       </c>
       <c r="C54">
-        <v>38.00366665087738</v>
+        <v>37.17879921129794</v>
       </c>
       <c r="D54">
-        <v>48.74366665087737</v>
+        <v>48.73879921129794</v>
       </c>
       <c r="E54">
-        <v>17.74</v>
+        <v>18.56</v>
       </c>
       <c r="F54">
-        <v>42.64</v>
+        <v>43.46</v>
       </c>
       <c r="G54">
         <v>31.9</v>
@@ -5709,28 +5709,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M54">
-        <v>3.232112</v>
+        <v>3.294268</v>
       </c>
       <c r="N54">
-        <v>3.507887999999999</v>
+        <v>3.445731999999999</v>
       </c>
       <c r="O54">
-        <v>1.0523664</v>
+        <v>1.0337196</v>
       </c>
       <c r="P54">
-        <v>2.455521599999999</v>
+        <v>2.412012399999999</v>
       </c>
       <c r="Q54">
-        <v>7.315521599999999</v>
+        <v>7.272012399999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.07811319598039551</v>
+        <v>0.07868340968379062</v>
       </c>
       <c r="T54">
-        <v>0.7462631866142153</v>
+        <v>0.7594320943138713</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.085323775908755</v>
+        <v>2.045978044287835</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0651030025513816</v>
+        <v>0.06512047103217335</v>
       </c>
       <c r="C55">
-        <v>37.17879921129794</v>
+        <v>36.35393274372592</v>
       </c>
       <c r="D55">
-        <v>48.73879921129794</v>
+        <v>48.73393274372592</v>
       </c>
       <c r="E55">
-        <v>18.56</v>
+        <v>19.38</v>
       </c>
       <c r="F55">
-        <v>43.46</v>
+        <v>44.28</v>
       </c>
       <c r="G55">
         <v>31.9</v>
@@ -5791,28 +5791,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M55">
-        <v>3.294268</v>
+        <v>3.356424000000001</v>
       </c>
       <c r="N55">
-        <v>3.445731999999999</v>
+        <v>3.383575999999999</v>
       </c>
       <c r="O55">
-        <v>1.0337196</v>
+        <v>1.0150728</v>
       </c>
       <c r="P55">
-        <v>2.412012399999999</v>
+        <v>2.368503199999999</v>
       </c>
       <c r="Q55">
-        <v>7.272012399999999</v>
+        <v>7.2285032</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.07868340968379062</v>
+        <v>0.07927841528733334</v>
       </c>
       <c r="T55">
-        <v>0.7594320943138713</v>
+        <v>0.77317356321786</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.045978044287835</v>
+        <v>2.008089561986209</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06512047103217335</v>
+        <v>0.07060493951296506</v>
       </c>
       <c r="C56">
-        <v>36.35393274372592</v>
+        <v>34.05262809765205</v>
       </c>
       <c r="D56">
-        <v>48.73393274372592</v>
+        <v>47.25262809765206</v>
       </c>
       <c r="E56">
-        <v>19.38</v>
+        <v>20.2</v>
       </c>
       <c r="F56">
-        <v>44.28</v>
+        <v>45.1</v>
       </c>
       <c r="G56">
         <v>31.9</v>
@@ -5873,45 +5873,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M56">
-        <v>3.356424000000001</v>
+        <v>4.059</v>
       </c>
       <c r="N56">
-        <v>3.383575999999999</v>
+        <v>2.680999999999999</v>
       </c>
       <c r="O56">
-        <v>1.0150728</v>
+        <v>0.8042999999999997</v>
       </c>
       <c r="P56">
-        <v>2.368503199999999</v>
+        <v>1.8767</v>
       </c>
       <c r="Q56">
-        <v>7.2285032</v>
+        <v>6.7367</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.07927841528733334</v>
+        <v>0.07989986558436683</v>
       </c>
       <c r="T56">
-        <v>0.77317356321786</v>
+        <v>0.7875257640731372</v>
       </c>
       <c r="U56">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V56">
         <v>0.3</v>
       </c>
       <c r="W56">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.008089561986209</v>
+        <v>1.660507514166051</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07060493951296506</v>
+        <v>0.07072180799375682</v>
       </c>
       <c r="C57">
-        <v>34.05262809765205</v>
+        <v>33.20204224834912</v>
       </c>
       <c r="D57">
-        <v>47.25262809765206</v>
+        <v>47.22204224834911</v>
       </c>
       <c r="E57">
-        <v>20.2</v>
+        <v>21.02</v>
       </c>
       <c r="F57">
-        <v>45.1</v>
+        <v>45.92</v>
       </c>
       <c r="G57">
         <v>31.9</v>
@@ -5955,28 +5955,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M57">
-        <v>4.059</v>
+        <v>4.1328</v>
       </c>
       <c r="N57">
-        <v>2.680999999999999</v>
+        <v>2.6072</v>
       </c>
       <c r="O57">
-        <v>0.8042999999999997</v>
+        <v>0.7821599999999999</v>
       </c>
       <c r="P57">
-        <v>1.8767</v>
+        <v>1.82504</v>
       </c>
       <c r="Q57">
-        <v>6.7367</v>
+        <v>6.685040000000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.07989986558436683</v>
+        <v>0.08054956362217458</v>
       </c>
       <c r="T57">
-        <v>0.7875257640731372</v>
+        <v>0.8025303376945634</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.660507514166051</v>
+        <v>1.630855594270229</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07072180799375682</v>
+        <v>0.07083867647454856</v>
       </c>
       <c r="C58">
-        <v>33.20204224834912</v>
+        <v>32.35149596886807</v>
       </c>
       <c r="D58">
-        <v>47.22204224834911</v>
+        <v>47.19149596886808</v>
       </c>
       <c r="E58">
-        <v>21.02</v>
+        <v>21.84</v>
       </c>
       <c r="F58">
-        <v>45.92</v>
+        <v>46.74</v>
       </c>
       <c r="G58">
         <v>31.9</v>
@@ -6037,28 +6037,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M58">
-        <v>4.1328</v>
+        <v>4.2066</v>
       </c>
       <c r="N58">
-        <v>2.6072</v>
+        <v>2.533399999999999</v>
       </c>
       <c r="O58">
-        <v>0.7821599999999999</v>
+        <v>0.7600199999999998</v>
       </c>
       <c r="P58">
-        <v>1.82504</v>
+        <v>1.77338</v>
       </c>
       <c r="Q58">
-        <v>6.685040000000001</v>
+        <v>6.63338</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.08054956362217458</v>
+        <v>0.08122948017336876</v>
       </c>
       <c r="T58">
-        <v>0.8025303376945634</v>
+        <v>0.8182327984611721</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.630855594270229</v>
+        <v>1.602244092616365</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07083867647454856</v>
+        <v>0.0709555449553403</v>
       </c>
       <c r="C59">
-        <v>32.35149596886807</v>
+        <v>31.5009891824696</v>
       </c>
       <c r="D59">
-        <v>47.19149596886808</v>
+        <v>47.16098918246961</v>
       </c>
       <c r="E59">
-        <v>21.84</v>
+        <v>22.66</v>
       </c>
       <c r="F59">
-        <v>46.74</v>
+        <v>47.56</v>
       </c>
       <c r="G59">
         <v>31.9</v>
@@ -6119,28 +6119,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M59">
-        <v>4.2066</v>
+        <v>4.2804</v>
       </c>
       <c r="N59">
-        <v>2.533399999999999</v>
+        <v>2.459599999999999</v>
       </c>
       <c r="O59">
-        <v>0.7600199999999998</v>
+        <v>0.7378799999999998</v>
       </c>
       <c r="P59">
-        <v>1.77338</v>
+        <v>1.721719999999999</v>
       </c>
       <c r="Q59">
-        <v>6.63338</v>
+        <v>6.58172</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.08122948017336876</v>
+        <v>0.0819417737031912</v>
       </c>
       <c r="T59">
-        <v>0.8182327984611721</v>
+        <v>0.8346829954547622</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.602244092616365</v>
+        <v>1.574619194467807</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0709555449553403</v>
+        <v>0.07107241343613205</v>
       </c>
       <c r="C60">
-        <v>31.5009891824696</v>
+        <v>30.65052181261268</v>
       </c>
       <c r="D60">
-        <v>47.16098918246961</v>
+        <v>47.13052181261267</v>
       </c>
       <c r="E60">
-        <v>22.66</v>
+        <v>23.48</v>
       </c>
       <c r="F60">
-        <v>47.56</v>
+        <v>48.38</v>
       </c>
       <c r="G60">
         <v>31.9</v>
@@ -6201,28 +6201,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M60">
-        <v>4.280399999999999</v>
+        <v>4.3542</v>
       </c>
       <c r="N60">
-        <v>2.4596</v>
+        <v>2.3858</v>
       </c>
       <c r="O60">
-        <v>0.73788</v>
+        <v>0.7157399999999999</v>
       </c>
       <c r="P60">
-        <v>1.72172</v>
+        <v>1.67006</v>
       </c>
       <c r="Q60">
-        <v>6.581720000000001</v>
+        <v>6.530060000000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.0819417737031912</v>
+        <v>0.08268881325885863</v>
       </c>
       <c r="T60">
-        <v>0.834682995454762</v>
+        <v>0.8519356410821858</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.574619194467807</v>
+        <v>1.547930733544624</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07107241343613205</v>
+        <v>0.07118928191692378</v>
       </c>
       <c r="C61">
-        <v>30.65052181261268</v>
+        <v>29.80009378295389</v>
       </c>
       <c r="D61">
-        <v>47.13052181261267</v>
+        <v>47.10009378295388</v>
       </c>
       <c r="E61">
-        <v>23.48</v>
+        <v>24.3</v>
       </c>
       <c r="F61">
-        <v>48.38</v>
+        <v>49.2</v>
       </c>
       <c r="G61">
         <v>31.9</v>
@@ -6283,28 +6283,28 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M61">
-        <v>4.3542</v>
+        <v>4.427999999999999</v>
       </c>
       <c r="N61">
-        <v>2.3858</v>
+        <v>2.312</v>
       </c>
       <c r="O61">
-        <v>0.7157399999999999</v>
+        <v>0.6936000000000001</v>
       </c>
       <c r="P61">
-        <v>1.67006</v>
+        <v>1.6184</v>
       </c>
       <c r="Q61">
-        <v>6.530060000000001</v>
+        <v>6.478400000000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.08268881325885863</v>
+        <v>0.08347320479230946</v>
       </c>
       <c r="T61">
-        <v>0.8519356410821858</v>
+        <v>0.8700509189909809</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.547930733544624</v>
+        <v>1.522131887985547</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07118928191692378</v>
+        <v>0.09804175505034854</v>
       </c>
       <c r="C62">
-        <v>29.80009378295389</v>
+        <v>22.89580627461378</v>
       </c>
       <c r="D62">
-        <v>47.10009378295388</v>
+        <v>41.01580627461377</v>
       </c>
       <c r="E62">
-        <v>24.3</v>
+        <v>25.12</v>
       </c>
       <c r="F62">
-        <v>49.2</v>
+        <v>50.02</v>
       </c>
       <c r="G62">
         <v>31.9</v>
@@ -6365,45 +6365,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M62">
-        <v>4.427999999999999</v>
+        <v>7.342936</v>
       </c>
       <c r="N62">
-        <v>2.312</v>
+        <v>-0.6029360000000006</v>
       </c>
       <c r="O62">
-        <v>0.6936000000000001</v>
+        <v>-0.1808808000000002</v>
       </c>
       <c r="P62">
-        <v>1.6184</v>
+        <v>-0.4220552000000004</v>
       </c>
       <c r="Q62">
-        <v>6.478400000000001</v>
+        <v>4.4379448</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.08347320479230946</v>
+        <v>0.08500587598901124</v>
       </c>
       <c r="T62">
-        <v>0.8700509189909809</v>
+        <v>0.9054474824252022</v>
       </c>
       <c r="U62">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.3</v>
+        <v>0.2753666925600332</v>
       </c>
       <c r="W62">
-        <v>0.063</v>
+        <v>0.1063761695321871</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.522131887985547</v>
+        <v>0.9178889752001106</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09804175505034854</v>
+        <v>0.09905175505034854</v>
       </c>
       <c r="C63">
-        <v>22.89580627461378</v>
+        <v>21.8774841019565</v>
       </c>
       <c r="D63">
-        <v>41.01580627461377</v>
+        <v>40.8174841019565</v>
       </c>
       <c r="E63">
-        <v>25.12</v>
+        <v>25.94</v>
       </c>
       <c r="F63">
-        <v>50.02</v>
+        <v>50.84</v>
       </c>
       <c r="G63">
         <v>31.9</v>
@@ -6447,37 +6447,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M63">
-        <v>7.342936</v>
+        <v>7.463312</v>
       </c>
       <c r="N63">
-        <v>-0.6029360000000006</v>
+        <v>-0.7233120000000008</v>
       </c>
       <c r="O63">
-        <v>-0.1808808000000002</v>
+        <v>-0.2169936000000003</v>
       </c>
       <c r="P63">
-        <v>-0.4220552000000004</v>
+        <v>-0.5063184000000006</v>
       </c>
       <c r="Q63">
-        <v>4.4379448</v>
+        <v>4.3536816</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.08500587598901124</v>
+        <v>0.08603760956766943</v>
       </c>
       <c r="T63">
-        <v>0.9054474824252022</v>
+        <v>0.9292750477521809</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2753666925600332</v>
+        <v>0.2709252942929358</v>
       </c>
       <c r="W63">
-        <v>0.1063761695321871</v>
+        <v>0.107028166797797</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.9178889752001106</v>
+        <v>0.9030843143097862</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09905175505034854</v>
+        <v>0.1000617550503485</v>
       </c>
       <c r="C64">
-        <v>21.8774841019565</v>
+        <v>20.86107057983482</v>
       </c>
       <c r="D64">
-        <v>40.8174841019565</v>
+        <v>40.62107057983482</v>
       </c>
       <c r="E64">
-        <v>25.94</v>
+        <v>26.76000000000001</v>
       </c>
       <c r="F64">
-        <v>50.84</v>
+        <v>51.66</v>
       </c>
       <c r="G64">
         <v>31.9</v>
@@ -6529,37 +6529,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M64">
-        <v>7.463312</v>
+        <v>7.583688000000001</v>
       </c>
       <c r="N64">
-        <v>-0.7233120000000008</v>
+        <v>-0.843688000000002</v>
       </c>
       <c r="O64">
-        <v>-0.2169936000000003</v>
+        <v>-0.2531064000000006</v>
       </c>
       <c r="P64">
-        <v>-0.5063184000000006</v>
+        <v>-0.5905816000000015</v>
       </c>
       <c r="Q64">
-        <v>4.3536816</v>
+        <v>4.269418399999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.08603760956766943</v>
+        <v>0.0871251125289578</v>
       </c>
       <c r="T64">
-        <v>0.9292750477521809</v>
+        <v>0.9543905895833212</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2709252942929358</v>
+        <v>0.2666248927962225</v>
       </c>
       <c r="W64">
-        <v>0.107028166797797</v>
+        <v>0.1076594657375145</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9030843143097862</v>
+        <v>0.8887496426540752</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1000617550503485</v>
+        <v>0.1010717550503485</v>
       </c>
       <c r="C65">
-        <v>20.86107057983482</v>
+        <v>19.84653828695041</v>
       </c>
       <c r="D65">
-        <v>40.62107057983482</v>
+        <v>40.4265382869504</v>
       </c>
       <c r="E65">
-        <v>26.76000000000001</v>
+        <v>27.58000000000001</v>
       </c>
       <c r="F65">
-        <v>51.66</v>
+        <v>52.48</v>
       </c>
       <c r="G65">
         <v>31.9</v>
@@ -6611,37 +6611,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M65">
-        <v>7.583688000000001</v>
+        <v>7.704064000000002</v>
       </c>
       <c r="N65">
-        <v>-0.843688000000002</v>
+        <v>-0.9640640000000023</v>
       </c>
       <c r="O65">
-        <v>-0.2531064000000006</v>
+        <v>-0.2892192000000007</v>
       </c>
       <c r="P65">
-        <v>-0.5905816000000015</v>
+        <v>-0.6748448000000016</v>
       </c>
       <c r="Q65">
-        <v>4.269418399999999</v>
+        <v>4.185155199999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.0871251125289578</v>
+        <v>0.08827303232142884</v>
       </c>
       <c r="T65">
-        <v>0.9543905895833212</v>
+        <v>0.9809014392939689</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2666248927962225</v>
+        <v>0.2624588788462816</v>
       </c>
       <c r="W65">
-        <v>0.1076594657375145</v>
+        <v>0.1082710365853659</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8887496426540752</v>
+        <v>0.8748629294876052</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1010717550503485</v>
+        <v>0.1020817550503486</v>
       </c>
       <c r="C66">
-        <v>19.84653828695041</v>
+        <v>18.83386032477834</v>
       </c>
       <c r="D66">
-        <v>40.4265382869504</v>
+        <v>40.23386032477834</v>
       </c>
       <c r="E66">
-        <v>27.58000000000001</v>
+        <v>28.40000000000001</v>
       </c>
       <c r="F66">
-        <v>52.48</v>
+        <v>53.3</v>
       </c>
       <c r="G66">
         <v>31.9</v>
@@ -6693,37 +6693,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M66">
-        <v>7.704064000000002</v>
+        <v>7.824440000000001</v>
       </c>
       <c r="N66">
-        <v>-0.9640640000000023</v>
+        <v>-1.084440000000002</v>
       </c>
       <c r="O66">
-        <v>-0.2892192000000007</v>
+        <v>-0.3253320000000005</v>
       </c>
       <c r="P66">
-        <v>-0.6748448000000016</v>
+        <v>-0.7591080000000012</v>
       </c>
       <c r="Q66">
-        <v>4.185155199999999</v>
+        <v>4.100891999999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.08827303232142884</v>
+        <v>0.08948654753061253</v>
       </c>
       <c r="T66">
-        <v>0.9809014392939689</v>
+        <v>1.008927194702368</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2624588788462816</v>
+        <v>0.2584210499409542</v>
       </c>
       <c r="W66">
-        <v>0.1082710365853659</v>
+        <v>0.1088637898686679</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8748629294876052</v>
+        <v>0.8614034998031807</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1020817550503486</v>
+        <v>0.1030917550503486</v>
       </c>
       <c r="C67">
-        <v>18.83386032477834</v>
+        <v>17.82301030516818</v>
       </c>
       <c r="D67">
-        <v>40.23386032477834</v>
+        <v>40.04301030516819</v>
       </c>
       <c r="E67">
-        <v>28.40000000000001</v>
+        <v>29.22000000000001</v>
       </c>
       <c r="F67">
-        <v>53.3</v>
+        <v>54.12</v>
       </c>
       <c r="G67">
         <v>31.9</v>
@@ -6775,37 +6775,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M67">
-        <v>7.824440000000001</v>
+        <v>7.944816000000001</v>
       </c>
       <c r="N67">
-        <v>-1.084440000000002</v>
+        <v>-1.204816000000002</v>
       </c>
       <c r="O67">
-        <v>-0.3253320000000005</v>
+        <v>-0.3614448000000006</v>
       </c>
       <c r="P67">
-        <v>-0.7591080000000012</v>
+        <v>-0.8433712000000013</v>
       </c>
       <c r="Q67">
-        <v>4.100891999999999</v>
+        <v>4.016628799999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.08948654753061253</v>
+        <v>0.09077144598739526</v>
       </c>
       <c r="T67">
-        <v>1.008927194702368</v>
+        <v>1.03860152395832</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2584210499409542</v>
+        <v>0.2545055794873033</v>
       </c>
       <c r="W67">
-        <v>0.1088637898686679</v>
+        <v>0.1094385809312639</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8614034998031807</v>
+        <v>0.8483519316243445</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1030917550503486</v>
+        <v>0.1041017550503485</v>
       </c>
       <c r="C68">
-        <v>17.82301030516818</v>
+        <v>16.81396233829633</v>
       </c>
       <c r="D68">
-        <v>40.04301030516819</v>
+        <v>39.85396233829633</v>
       </c>
       <c r="E68">
-        <v>29.22000000000001</v>
+        <v>30.04000000000001</v>
       </c>
       <c r="F68">
-        <v>54.12</v>
+        <v>54.94</v>
       </c>
       <c r="G68">
         <v>31.9</v>
@@ -6857,37 +6857,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M68">
-        <v>7.944816000000001</v>
+        <v>8.065192000000001</v>
       </c>
       <c r="N68">
-        <v>-1.204816000000002</v>
+        <v>-1.325192000000002</v>
       </c>
       <c r="O68">
-        <v>-0.3614448000000006</v>
+        <v>-0.3975576000000006</v>
       </c>
       <c r="P68">
-        <v>-0.8433712000000013</v>
+        <v>-0.9276344000000015</v>
       </c>
       <c r="Q68">
-        <v>4.016628799999999</v>
+        <v>3.932365599999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.09077144598739526</v>
+        <v>0.09213421707792238</v>
       </c>
       <c r="T68">
-        <v>1.03860152395832</v>
+        <v>1.070074297411603</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2545055794873033</v>
+        <v>0.2507069887486869</v>
       </c>
       <c r="W68">
-        <v>0.1094385809312639</v>
+        <v>0.1099962140516928</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8483519316243445</v>
+        <v>0.8356899624956229</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1041017550503485</v>
+        <v>0.1051117550503485</v>
       </c>
       <c r="C69">
-        <v>16.81396233829633</v>
+        <v>15.80669102095784</v>
       </c>
       <c r="D69">
-        <v>39.85396233829633</v>
+        <v>39.66669102095786</v>
       </c>
       <c r="E69">
-        <v>30.04000000000001</v>
+        <v>30.86000000000001</v>
       </c>
       <c r="F69">
-        <v>54.94</v>
+        <v>55.76000000000001</v>
       </c>
       <c r="G69">
         <v>31.9</v>
@@ -6939,37 +6939,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M69">
-        <v>8.065192000000001</v>
+        <v>8.185568000000002</v>
       </c>
       <c r="N69">
-        <v>-1.325192000000002</v>
+        <v>-1.445568000000002</v>
       </c>
       <c r="O69">
-        <v>-0.3975576000000006</v>
+        <v>-0.4336704000000007</v>
       </c>
       <c r="P69">
-        <v>-0.9276344000000015</v>
+        <v>-1.011897600000002</v>
       </c>
       <c r="Q69">
-        <v>3.932365599999999</v>
+        <v>3.848102399999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.09213421707792238</v>
+        <v>0.09358216136160746</v>
       </c>
       <c r="T69">
-        <v>1.070074297411603</v>
+        <v>1.103514119205715</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2507069887486869</v>
+        <v>0.2470201212670885</v>
       </c>
       <c r="W69">
-        <v>0.1099962140516928</v>
+        <v>0.1105374461979914</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8356899624956229</v>
+        <v>0.8234004042236285</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1051117550503485</v>
+        <v>0.1061217550503486</v>
       </c>
       <c r="C70">
-        <v>15.80669102095784</v>
+        <v>14.80117142518717</v>
       </c>
       <c r="D70">
-        <v>39.66669102095786</v>
+        <v>39.48117142518717</v>
       </c>
       <c r="E70">
-        <v>30.86000000000001</v>
+        <v>31.68000000000001</v>
       </c>
       <c r="F70">
-        <v>55.76000000000001</v>
+        <v>56.58000000000001</v>
       </c>
       <c r="G70">
         <v>31.9</v>
@@ -7021,37 +7021,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M70">
-        <v>8.185568000000002</v>
+        <v>8.305944000000002</v>
       </c>
       <c r="N70">
-        <v>-1.445568000000002</v>
+        <v>-1.565944000000003</v>
       </c>
       <c r="O70">
-        <v>-0.4336704000000007</v>
+        <v>-0.4697832000000008</v>
       </c>
       <c r="P70">
-        <v>-1.011897600000002</v>
+        <v>-1.096160800000002</v>
       </c>
       <c r="Q70">
-        <v>3.848102399999998</v>
+        <v>3.763839199999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.09358216136160746</v>
+        <v>0.09512352140553028</v>
       </c>
       <c r="T70">
-        <v>1.103514119205715</v>
+        <v>1.139111348857512</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2470201212670885</v>
+        <v>0.2434401195095945</v>
       </c>
       <c r="W70">
-        <v>0.1105374461979914</v>
+        <v>0.1110629904559915</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8234004042236285</v>
+        <v>0.8114670650319816</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1061217550503486</v>
+        <v>0.1457618924876994</v>
       </c>
       <c r="C71">
-        <v>14.80117142518717</v>
+        <v>7.857985943467099</v>
       </c>
       <c r="D71">
-        <v>39.48117142518717</v>
+        <v>33.35798594346711</v>
       </c>
       <c r="E71">
-        <v>31.68000000000001</v>
+        <v>32.50000000000001</v>
       </c>
       <c r="F71">
-        <v>56.58000000000001</v>
+        <v>57.40000000000001</v>
       </c>
       <c r="G71">
         <v>31.9</v>
@@ -7103,45 +7103,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M71">
-        <v>8.305944000000002</v>
+        <v>11.52592</v>
       </c>
       <c r="N71">
-        <v>-1.565944000000003</v>
+        <v>-4.785920000000002</v>
       </c>
       <c r="O71">
-        <v>-0.4697832000000008</v>
+        <v>-1.435776</v>
       </c>
       <c r="P71">
-        <v>-1.096160800000002</v>
+        <v>-3.350144000000001</v>
       </c>
       <c r="Q71">
-        <v>3.763839199999999</v>
+        <v>1.509855999999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.09512352140553028</v>
+        <v>0.09953476357688432</v>
       </c>
       <c r="T71">
-        <v>1.139111348857512</v>
+        <v>1.240987611475389</v>
       </c>
       <c r="U71">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.2434401195095945</v>
+        <v>0.1754306814553632</v>
       </c>
       <c r="W71">
-        <v>0.1110629904559915</v>
+        <v>0.1655735191637631</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.8114670650319816</v>
+        <v>0.584768938184544</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1457618924876994</v>
+        <v>0.1473118924876995</v>
       </c>
       <c r="C72">
-        <v>7.857985943467099</v>
+        <v>6.836910981535929</v>
       </c>
       <c r="D72">
-        <v>33.35798594346711</v>
+        <v>33.15691098153594</v>
       </c>
       <c r="E72">
-        <v>32.50000000000001</v>
+        <v>33.32000000000001</v>
       </c>
       <c r="F72">
-        <v>57.40000000000001</v>
+        <v>58.22000000000001</v>
       </c>
       <c r="G72">
         <v>31.9</v>
@@ -7185,37 +7185,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M72">
-        <v>11.52592</v>
+        <v>11.690576</v>
       </c>
       <c r="N72">
-        <v>-4.785920000000002</v>
+        <v>-4.950576000000003</v>
       </c>
       <c r="O72">
-        <v>-1.435776</v>
+        <v>-1.485172800000001</v>
       </c>
       <c r="P72">
-        <v>-3.350144000000001</v>
+        <v>-3.465403200000002</v>
       </c>
       <c r="Q72">
-        <v>1.509855999999999</v>
+        <v>1.394596799999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.09953476357688432</v>
+        <v>0.1013876864588459</v>
       </c>
       <c r="T72">
-        <v>1.240987611475389</v>
+        <v>1.283780287733161</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1754306814553632</v>
+        <v>0.1729598267869778</v>
       </c>
       <c r="W72">
-        <v>0.1655735191637631</v>
+        <v>0.1660696667811749</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.584768938184544</v>
+        <v>0.5765327559565926</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1473118924876994</v>
+        <v>0.1488618924876994</v>
       </c>
       <c r="C73">
-        <v>6.836910981535937</v>
+        <v>5.818245570958418</v>
       </c>
       <c r="D73">
-        <v>33.15691098153594</v>
+        <v>32.95824557095842</v>
       </c>
       <c r="E73">
-        <v>33.32</v>
+        <v>34.14</v>
       </c>
       <c r="F73">
-        <v>58.22</v>
+        <v>59.04</v>
       </c>
       <c r="G73">
         <v>31.9</v>
@@ -7267,37 +7267,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M73">
-        <v>11.690576</v>
+        <v>11.855232</v>
       </c>
       <c r="N73">
-        <v>-4.950576000000001</v>
+        <v>-5.115232000000002</v>
       </c>
       <c r="O73">
-        <v>-1.4851728</v>
+        <v>-1.5345696</v>
       </c>
       <c r="P73">
-        <v>-3.465403200000001</v>
+        <v>-3.580662400000001</v>
       </c>
       <c r="Q73">
-        <v>1.3945968</v>
+        <v>1.279337599999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1013876864588458</v>
+        <v>0.1033729609752332</v>
       </c>
       <c r="T73">
-        <v>1.28378028773316</v>
+        <v>1.32962958372363</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1729598267869778</v>
+        <v>0.170557606970492</v>
       </c>
       <c r="W73">
-        <v>0.1660696667811749</v>
+        <v>0.1665520325203252</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5765327559565927</v>
+        <v>0.5685253565683066</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1488618924876994</v>
+        <v>0.1504118924876995</v>
       </c>
       <c r="C74">
-        <v>5.818245570958418</v>
+        <v>4.80194665795814</v>
       </c>
       <c r="D74">
-        <v>32.95824557095842</v>
+        <v>32.76194665795815</v>
       </c>
       <c r="E74">
-        <v>34.14</v>
+        <v>34.96</v>
       </c>
       <c r="F74">
-        <v>59.04</v>
+        <v>59.86</v>
       </c>
       <c r="G74">
         <v>31.9</v>
@@ -7349,37 +7349,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M74">
-        <v>11.855232</v>
+        <v>12.019888</v>
       </c>
       <c r="N74">
-        <v>-5.115232000000002</v>
+        <v>-5.279888000000001</v>
       </c>
       <c r="O74">
-        <v>-1.5345696</v>
+        <v>-1.5839664</v>
       </c>
       <c r="P74">
-        <v>-3.580662400000001</v>
+        <v>-3.6959216</v>
       </c>
       <c r="Q74">
-        <v>1.279337599999999</v>
+        <v>1.1640784</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1033729609752332</v>
+        <v>0.1055052928632048</v>
       </c>
       <c r="T74">
-        <v>1.32962958372363</v>
+        <v>1.378875123861543</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.170557606970492</v>
+        <v>0.1682212013955538</v>
       </c>
       <c r="W74">
-        <v>0.1665520325203252</v>
+        <v>0.1670211827597728</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5685253565683066</v>
+        <v>0.5607373379851792</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1504118924876995</v>
+        <v>0.1519618924876994</v>
       </c>
       <c r="C75">
-        <v>4.80194665795814</v>
+        <v>3.787972208396887</v>
       </c>
       <c r="D75">
-        <v>32.76194665795815</v>
+        <v>32.56797220839689</v>
       </c>
       <c r="E75">
-        <v>34.96</v>
+        <v>35.78</v>
       </c>
       <c r="F75">
-        <v>59.86</v>
+        <v>60.68</v>
       </c>
       <c r="G75">
         <v>31.9</v>
@@ -7431,37 +7431,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M75">
-        <v>12.019888</v>
+        <v>12.184544</v>
       </c>
       <c r="N75">
-        <v>-5.279888000000001</v>
+        <v>-5.444544000000001</v>
       </c>
       <c r="O75">
-        <v>-1.5839664</v>
+        <v>-1.6333632</v>
       </c>
       <c r="P75">
-        <v>-3.6959216</v>
+        <v>-3.811180800000001</v>
       </c>
       <c r="Q75">
-        <v>1.1640784</v>
+        <v>1.0488192</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1055052928632048</v>
+        <v>0.1078016502810203</v>
       </c>
       <c r="T75">
-        <v>1.378875123861543</v>
+        <v>1.431908782471602</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1682212013955538</v>
+        <v>0.1659479419172355</v>
       </c>
       <c r="W75">
-        <v>0.1670211827597728</v>
+        <v>0.1674776532630191</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5607373379851792</v>
+        <v>0.5531598063907848</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1519618924876994</v>
+        <v>0.1535118924876994</v>
       </c>
       <c r="C76">
-        <v>3.787972208396887</v>
+        <v>2.776281177767231</v>
       </c>
       <c r="D76">
-        <v>32.56797220839689</v>
+        <v>32.37628117776723</v>
       </c>
       <c r="E76">
-        <v>35.78</v>
+        <v>36.6</v>
       </c>
       <c r="F76">
-        <v>60.68</v>
+        <v>61.5</v>
       </c>
       <c r="G76">
         <v>31.9</v>
@@ -7513,37 +7513,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M76">
-        <v>12.184544</v>
+        <v>12.3492</v>
       </c>
       <c r="N76">
-        <v>-5.444544000000001</v>
+        <v>-5.6092</v>
       </c>
       <c r="O76">
-        <v>-1.6333632</v>
+        <v>-1.68276</v>
       </c>
       <c r="P76">
-        <v>-3.811180800000001</v>
+        <v>-3.92644</v>
       </c>
       <c r="Q76">
-        <v>1.0488192</v>
+        <v>0.9335599999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1078016502810203</v>
+        <v>0.1102817162922612</v>
       </c>
       <c r="T76">
-        <v>1.431908782471602</v>
+        <v>1.489185133770466</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1659479419172355</v>
+        <v>0.1637353026916723</v>
       </c>
       <c r="W76">
-        <v>0.1674776532630191</v>
+        <v>0.1679219512195122</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5531598063907848</v>
+        <v>0.5457843423055744</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1535118924876994</v>
+        <v>0.1550618924876995</v>
       </c>
       <c r="C77">
-        <v>2.776281177767231</v>
+        <v>1.766833482238759</v>
       </c>
       <c r="D77">
-        <v>32.37628117776723</v>
+        <v>32.18683348223876</v>
       </c>
       <c r="E77">
-        <v>36.6</v>
+        <v>37.42</v>
       </c>
       <c r="F77">
-        <v>61.5</v>
+        <v>62.32</v>
       </c>
       <c r="G77">
         <v>31.9</v>
@@ -7595,37 +7595,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M77">
-        <v>12.3492</v>
+        <v>12.513856</v>
       </c>
       <c r="N77">
-        <v>-5.6092</v>
+        <v>-5.773856000000001</v>
       </c>
       <c r="O77">
-        <v>-1.68276</v>
+        <v>-1.7321568</v>
       </c>
       <c r="P77">
-        <v>-3.92644</v>
+        <v>-4.041699200000001</v>
       </c>
       <c r="Q77">
-        <v>0.9335599999999999</v>
+        <v>0.8183007999999994</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1102817162922612</v>
+        <v>0.1129684544711054</v>
       </c>
       <c r="T77">
-        <v>1.489185133770466</v>
+        <v>1.551234514344236</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1637353026916723</v>
+        <v>0.1615808908141503</v>
       </c>
       <c r="W77">
-        <v>0.1679219512195122</v>
+        <v>0.1683545571245186</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5457843423055744</v>
+        <v>0.538602969380501</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1550618924876995</v>
+        <v>0.1566118924876995</v>
       </c>
       <c r="C78">
-        <v>1.766833482238759</v>
+        <v>0.7595899707149556</v>
       </c>
       <c r="D78">
-        <v>32.18683348223876</v>
+        <v>31.99958997071496</v>
       </c>
       <c r="E78">
-        <v>37.42</v>
+        <v>38.24</v>
       </c>
       <c r="F78">
-        <v>62.32</v>
+        <v>63.14</v>
       </c>
       <c r="G78">
         <v>31.9</v>
@@ -7677,37 +7677,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M78">
-        <v>12.513856</v>
+        <v>12.678512</v>
       </c>
       <c r="N78">
-        <v>-5.773856000000001</v>
+        <v>-5.938512000000002</v>
       </c>
       <c r="O78">
-        <v>-1.7321568</v>
+        <v>-1.781553600000001</v>
       </c>
       <c r="P78">
-        <v>-4.041699200000001</v>
+        <v>-4.156958400000001</v>
       </c>
       <c r="Q78">
-        <v>0.8183007999999994</v>
+        <v>0.7030415999999988</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1129684544711054</v>
+        <v>0.1158888220568056</v>
       </c>
       <c r="T78">
-        <v>1.551234514344236</v>
+        <v>1.618679493228768</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1615808908141503</v>
+        <v>0.1594824376866938</v>
       </c>
       <c r="W78">
-        <v>0.1683545571245186</v>
+        <v>0.1687759265125119</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.538602969380501</v>
+        <v>0.5316081256223126</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1566118924876995</v>
+        <v>0.1581618924876994</v>
       </c>
       <c r="C79">
-        <v>0.7595899707149556</v>
+        <v>-0.2454876021404218</v>
       </c>
       <c r="D79">
-        <v>31.99958997071496</v>
+        <v>31.81451239785958</v>
       </c>
       <c r="E79">
-        <v>38.24</v>
+        <v>39.06</v>
       </c>
       <c r="F79">
-        <v>63.14</v>
+        <v>63.96</v>
       </c>
       <c r="G79">
         <v>31.9</v>
@@ -7759,37 +7759,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M79">
-        <v>12.678512</v>
+        <v>12.843168</v>
       </c>
       <c r="N79">
-        <v>-5.938512000000002</v>
+        <v>-6.103168000000001</v>
       </c>
       <c r="O79">
-        <v>-1.781553600000001</v>
+        <v>-1.8309504</v>
       </c>
       <c r="P79">
-        <v>-4.156958400000001</v>
+        <v>-4.272217600000001</v>
       </c>
       <c r="Q79">
-        <v>0.7030415999999988</v>
+        <v>0.5877823999999991</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1158888220568056</v>
+        <v>0.1190746776048422</v>
       </c>
       <c r="T79">
-        <v>1.618679493228768</v>
+        <v>1.692255833830075</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1594824376866938</v>
+        <v>0.1574377910496849</v>
       </c>
       <c r="W79">
-        <v>0.1687759265125119</v>
+        <v>0.1691864915572233</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5316081256223126</v>
+        <v>0.5247926368322831</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1581618924876994</v>
+        <v>0.1597118924876995</v>
       </c>
       <c r="C80">
-        <v>-0.2454876021404218</v>
+        <v>-1.248436601946068</v>
       </c>
       <c r="D80">
-        <v>31.81451239785958</v>
+        <v>31.63156339805393</v>
       </c>
       <c r="E80">
-        <v>39.06</v>
+        <v>39.88</v>
       </c>
       <c r="F80">
-        <v>63.96</v>
+        <v>64.78</v>
       </c>
       <c r="G80">
         <v>31.9</v>
@@ -7841,37 +7841,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M80">
-        <v>12.843168</v>
+        <v>13.007824</v>
       </c>
       <c r="N80">
-        <v>-6.103168000000001</v>
+        <v>-6.267824000000002</v>
       </c>
       <c r="O80">
-        <v>-1.8309504</v>
+        <v>-1.880347200000001</v>
       </c>
       <c r="P80">
-        <v>-4.272217600000001</v>
+        <v>-4.387476800000002</v>
       </c>
       <c r="Q80">
-        <v>0.5877823999999991</v>
+        <v>0.4725231999999986</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1190746776048422</v>
+        <v>0.1225639479669776</v>
       </c>
       <c r="T80">
-        <v>1.692255833830075</v>
+        <v>1.772839444964841</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1574377910496849</v>
+        <v>0.1554449076186762</v>
       </c>
       <c r="W80">
-        <v>0.1691864915572233</v>
+        <v>0.1695866625501698</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5247926368322831</v>
+        <v>0.5181496920622541</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1597118924876995</v>
+        <v>0.1612618924876995</v>
       </c>
       <c r="C81">
-        <v>-1.248436601946068</v>
+        <v>-2.249293539752557</v>
       </c>
       <c r="D81">
-        <v>31.63156339805393</v>
+        <v>31.45070646024746</v>
       </c>
       <c r="E81">
-        <v>39.88</v>
+        <v>40.70000000000001</v>
       </c>
       <c r="F81">
-        <v>64.78</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="G81">
         <v>31.9</v>
@@ -7923,37 +7923,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M81">
-        <v>13.007824</v>
+        <v>13.17248</v>
       </c>
       <c r="N81">
-        <v>-6.267824000000002</v>
+        <v>-6.432480000000003</v>
       </c>
       <c r="O81">
-        <v>-1.880347200000001</v>
+        <v>-1.929744000000001</v>
       </c>
       <c r="P81">
-        <v>-4.387476800000002</v>
+        <v>-4.502736000000002</v>
       </c>
       <c r="Q81">
-        <v>0.4725231999999986</v>
+        <v>0.357263999999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1225639479669776</v>
+        <v>0.1264021453653265</v>
       </c>
       <c r="T81">
-        <v>1.772839444964841</v>
+        <v>1.861481417213083</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1554449076186762</v>
+        <v>0.1535018462734428</v>
       </c>
       <c r="W81">
-        <v>0.1695866625501698</v>
+        <v>0.1699768292682927</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5181496920622541</v>
+        <v>0.5116728209114759</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1612618924876995</v>
+        <v>0.1628118924876994</v>
       </c>
       <c r="C82">
-        <v>-2.249293539752557</v>
+        <v>-3.248094096333872</v>
       </c>
       <c r="D82">
-        <v>31.45070646024746</v>
+        <v>31.27190590366613</v>
       </c>
       <c r="E82">
-        <v>40.70000000000001</v>
+        <v>41.52</v>
       </c>
       <c r="F82">
-        <v>65.60000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="G82">
         <v>31.9</v>
@@ -8005,37 +8005,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M82">
-        <v>13.17248</v>
+        <v>13.337136</v>
       </c>
       <c r="N82">
-        <v>-6.432480000000003</v>
+        <v>-6.597136000000002</v>
       </c>
       <c r="O82">
-        <v>-1.929744000000001</v>
+        <v>-1.9791408</v>
       </c>
       <c r="P82">
-        <v>-4.502736000000002</v>
+        <v>-4.617995200000001</v>
       </c>
       <c r="Q82">
-        <v>0.357263999999998</v>
+        <v>0.2420047999999992</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1264021453653265</v>
+        <v>0.130644363542449</v>
       </c>
       <c r="T82">
-        <v>1.861481417213083</v>
+        <v>1.959454123382193</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1535018462734428</v>
+        <v>0.1516067617515484</v>
       </c>
       <c r="W82">
-        <v>0.1699768292682927</v>
+        <v>0.1703573622402891</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5116728209114759</v>
+        <v>0.5053558725051615</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1628118924876994</v>
+        <v>0.1933968629706188</v>
       </c>
       <c r="C83">
-        <v>-3.248094096333872</v>
+        <v>-7.222329917638376</v>
       </c>
       <c r="D83">
-        <v>31.27190590366613</v>
+        <v>28.11767008236164</v>
       </c>
       <c r="E83">
-        <v>41.52</v>
+        <v>42.34000000000001</v>
       </c>
       <c r="F83">
-        <v>66.42</v>
+        <v>67.24000000000001</v>
       </c>
       <c r="G83">
         <v>31.9</v>
@@ -8087,45 +8087,45 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M83">
-        <v>13.337136</v>
+        <v>15.855192</v>
       </c>
       <c r="N83">
-        <v>-6.597136000000002</v>
+        <v>-9.115192000000004</v>
       </c>
       <c r="O83">
-        <v>-1.9791408</v>
+        <v>-2.734557600000001</v>
       </c>
       <c r="P83">
-        <v>-4.617995200000001</v>
+        <v>-6.380634400000003</v>
       </c>
       <c r="Q83">
-        <v>0.2420047999999992</v>
+        <v>-1.520634400000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.130644363542449</v>
+        <v>0.1372188864221371</v>
       </c>
       <c r="T83">
-        <v>1.959454123382193</v>
+        <v>2.111290679495083</v>
       </c>
       <c r="U83">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1516067617515484</v>
+        <v>0.1275292030522241</v>
       </c>
       <c r="W83">
-        <v>0.1703573622402891</v>
+        <v>0.2057286139202855</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.5053558725051615</v>
+        <v>0.4250973435074137</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1933968629706188</v>
+        <v>0.1952968629706189</v>
       </c>
       <c r="C84">
-        <v>-7.222329917638376</v>
+        <v>-8.217416113790875</v>
       </c>
       <c r="D84">
-        <v>28.11767008236164</v>
+        <v>27.94258388620913</v>
       </c>
       <c r="E84">
-        <v>42.34000000000001</v>
+        <v>43.16</v>
       </c>
       <c r="F84">
-        <v>67.24000000000001</v>
+        <v>68.06</v>
       </c>
       <c r="G84">
         <v>31.9</v>
@@ -8169,37 +8169,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M84">
-        <v>15.855192</v>
+        <v>16.048548</v>
       </c>
       <c r="N84">
-        <v>-9.115192000000004</v>
+        <v>-9.308548000000002</v>
       </c>
       <c r="O84">
-        <v>-2.734557600000001</v>
+        <v>-2.7925644</v>
       </c>
       <c r="P84">
-        <v>-6.380634400000003</v>
+        <v>-6.515983600000002</v>
       </c>
       <c r="Q84">
-        <v>-1.520634400000003</v>
+        <v>-1.655983600000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1372188864221371</v>
+        <v>0.1425964679763805</v>
       </c>
       <c r="T84">
-        <v>2.111290679495083</v>
+        <v>2.235484248877147</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1275292030522241</v>
+        <v>0.1259927066299082</v>
       </c>
       <c r="W84">
-        <v>0.2057286139202855</v>
+        <v>0.2060909197766677</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4250973435074137</v>
+        <v>0.4199756887663606</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1952968629706189</v>
+        <v>0.1971968629706188</v>
       </c>
       <c r="C85">
-        <v>-8.217416113790875</v>
+        <v>-9.21033531173498</v>
       </c>
       <c r="D85">
-        <v>27.94258388620913</v>
+        <v>27.76966468826503</v>
       </c>
       <c r="E85">
-        <v>43.16</v>
+        <v>43.98000000000001</v>
       </c>
       <c r="F85">
-        <v>68.06</v>
+        <v>68.88000000000001</v>
       </c>
       <c r="G85">
         <v>31.9</v>
@@ -8251,37 +8251,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M85">
-        <v>16.048548</v>
+        <v>16.241904</v>
       </c>
       <c r="N85">
-        <v>-9.308548000000002</v>
+        <v>-9.501904000000003</v>
       </c>
       <c r="O85">
-        <v>-2.7925644</v>
+        <v>-2.850571200000001</v>
       </c>
       <c r="P85">
-        <v>-6.515983600000002</v>
+        <v>-6.651332800000002</v>
       </c>
       <c r="Q85">
-        <v>-1.655983600000002</v>
+        <v>-1.791332800000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1425964679763805</v>
+        <v>0.1486462472249042</v>
       </c>
       <c r="T85">
-        <v>2.235484248877147</v>
+        <v>2.375202014431969</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1259927066299082</v>
+        <v>0.1244927934557426</v>
       </c>
       <c r="W85">
-        <v>0.2060909197766677</v>
+        <v>0.2064445993031359</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4199756887663606</v>
+        <v>0.4149759781858087</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1971968629706188</v>
+        <v>0.1990968629706188</v>
       </c>
       <c r="C86">
-        <v>-9.210335311734966</v>
+        <v>-10.20112749463487</v>
       </c>
       <c r="D86">
-        <v>27.76966468826503</v>
+        <v>27.59887250536514</v>
       </c>
       <c r="E86">
-        <v>43.98</v>
+        <v>44.8</v>
       </c>
       <c r="F86">
-        <v>68.88</v>
+        <v>69.7</v>
       </c>
       <c r="G86">
         <v>31.9</v>
@@ -8333,37 +8333,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M86">
-        <v>16.241904</v>
+        <v>16.43526</v>
       </c>
       <c r="N86">
-        <v>-9.501904</v>
+        <v>-9.695260000000005</v>
       </c>
       <c r="O86">
-        <v>-2.8505712</v>
+        <v>-2.908578000000001</v>
       </c>
       <c r="P86">
-        <v>-6.6513328</v>
+        <v>-6.786682000000003</v>
       </c>
       <c r="Q86">
-        <v>-1.7913328</v>
+        <v>-1.926682000000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1486462472249042</v>
+        <v>0.1555026637065645</v>
       </c>
       <c r="T86">
-        <v>2.375202014431967</v>
+        <v>2.533548815394099</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1244927934557426</v>
+        <v>0.1230281723562633</v>
       </c>
       <c r="W86">
-        <v>0.2064445993031359</v>
+        <v>0.2067899569583931</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4149759781858087</v>
+        <v>0.4100939078542108</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1990968629706188</v>
+        <v>0.2009968629706188</v>
       </c>
       <c r="C87">
-        <v>-10.20112749463487</v>
+        <v>-11.18983166803125</v>
       </c>
       <c r="D87">
-        <v>27.59887250536514</v>
+        <v>27.43016833196875</v>
       </c>
       <c r="E87">
-        <v>44.8</v>
+        <v>45.62</v>
       </c>
       <c r="F87">
-        <v>69.7</v>
+        <v>70.52</v>
       </c>
       <c r="G87">
         <v>31.9</v>
@@ -8415,37 +8415,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M87">
-        <v>16.43526</v>
+        <v>16.628616</v>
       </c>
       <c r="N87">
-        <v>-9.695260000000005</v>
+        <v>-9.888616000000003</v>
       </c>
       <c r="O87">
-        <v>-2.908578000000001</v>
+        <v>-2.966584800000001</v>
       </c>
       <c r="P87">
-        <v>-6.786682000000003</v>
+        <v>-6.922031200000002</v>
       </c>
       <c r="Q87">
-        <v>-1.926682000000003</v>
+        <v>-2.062031200000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1555026637065645</v>
+        <v>0.1633385682570333</v>
       </c>
       <c r="T87">
-        <v>2.533548815394099</v>
+        <v>2.714516587922248</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1230281723562633</v>
+        <v>0.1215976122125858</v>
       </c>
       <c r="W87">
-        <v>0.2067899569583931</v>
+        <v>0.2071272830402723</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4100939078542108</v>
+        <v>0.4053253740419526</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2009968629706188</v>
+        <v>0.2028968629706188</v>
       </c>
       <c r="C88">
-        <v>-11.18983166803125</v>
+        <v>-12.17648588953948</v>
       </c>
       <c r="D88">
-        <v>27.43016833196875</v>
+        <v>27.26351411046053</v>
       </c>
       <c r="E88">
-        <v>45.62</v>
+        <v>46.44</v>
       </c>
       <c r="F88">
-        <v>70.52</v>
+        <v>71.34</v>
       </c>
       <c r="G88">
         <v>31.9</v>
@@ -8497,37 +8497,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M88">
-        <v>16.628616</v>
+        <v>16.821972</v>
       </c>
       <c r="N88">
-        <v>-9.888616000000003</v>
+        <v>-10.081972</v>
       </c>
       <c r="O88">
-        <v>-2.966584800000001</v>
+        <v>-3.024591600000001</v>
       </c>
       <c r="P88">
-        <v>-6.922031200000002</v>
+        <v>-7.057380400000003</v>
       </c>
       <c r="Q88">
-        <v>-2.062031200000002</v>
+        <v>-2.197380400000003</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1633385682570333</v>
+        <v>0.1723799965844975</v>
       </c>
       <c r="T88">
-        <v>2.714516587922248</v>
+        <v>2.92332555622396</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1215976122125858</v>
+        <v>0.1201999385089928</v>
       </c>
       <c r="W88">
-        <v>0.2071272830402723</v>
+        <v>0.2074568544995795</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4053253740419526</v>
+        <v>0.4006664616966428</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2028968629706188</v>
+        <v>0.2047968629706188</v>
       </c>
       <c r="C89">
-        <v>-12.17648588953948</v>
+        <v>-13.16112729747157</v>
       </c>
       <c r="D89">
-        <v>27.26351411046053</v>
+        <v>27.09887270252842</v>
       </c>
       <c r="E89">
-        <v>46.44</v>
+        <v>47.26</v>
       </c>
       <c r="F89">
-        <v>71.34</v>
+        <v>72.16</v>
       </c>
       <c r="G89">
         <v>31.9</v>
@@ -8579,37 +8579,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M89">
-        <v>16.821972</v>
+        <v>17.015328</v>
       </c>
       <c r="N89">
-        <v>-10.081972</v>
+        <v>-10.275328</v>
       </c>
       <c r="O89">
-        <v>-3.024591600000001</v>
+        <v>-3.082598400000001</v>
       </c>
       <c r="P89">
-        <v>-7.057380400000003</v>
+        <v>-7.192729600000002</v>
       </c>
       <c r="Q89">
-        <v>-2.197380400000003</v>
+        <v>-2.332729600000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1723799965844975</v>
+        <v>0.1829283296332056</v>
       </c>
       <c r="T89">
-        <v>2.92332555622396</v>
+        <v>3.166936019242624</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1201999385089928</v>
+        <v>0.1188340301168452</v>
       </c>
       <c r="W89">
-        <v>0.2074568544995795</v>
+        <v>0.2077789356984479</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4006664616966428</v>
+        <v>0.3961134337228174</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2047968629706188</v>
+        <v>0.2066968629706188</v>
       </c>
       <c r="C90">
-        <v>-13.16112729747157</v>
+        <v>-14.14379213842763</v>
       </c>
       <c r="D90">
-        <v>27.09887270252842</v>
+        <v>26.93620786157238</v>
       </c>
       <c r="E90">
-        <v>47.26</v>
+        <v>48.08000000000001</v>
       </c>
       <c r="F90">
-        <v>72.16</v>
+        <v>72.98</v>
       </c>
       <c r="G90">
         <v>31.9</v>
@@ -8661,37 +8661,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M90">
-        <v>17.015328</v>
+        <v>17.208684</v>
       </c>
       <c r="N90">
-        <v>-10.275328</v>
+        <v>-10.468684</v>
       </c>
       <c r="O90">
-        <v>-3.082598400000001</v>
+        <v>-3.140605200000001</v>
       </c>
       <c r="P90">
-        <v>-7.192729600000002</v>
+        <v>-7.328078800000002</v>
       </c>
       <c r="Q90">
-        <v>-2.332729600000001</v>
+        <v>-2.468078800000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.1829283296332056</v>
+        <v>0.1953945414180424</v>
       </c>
       <c r="T90">
-        <v>3.166936019242624</v>
+        <v>3.454839293719226</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1188340301168452</v>
+        <v>0.1174988162953076</v>
       </c>
       <c r="W90">
-        <v>0.2077789356984479</v>
+        <v>0.2080937791175665</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3961134337228174</v>
+        <v>0.3916627209843587</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2066968629706188</v>
+        <v>0.2085968629706188</v>
       </c>
       <c r="C91">
-        <v>-14.14379213842763</v>
+        <v>-15.12451579389911</v>
       </c>
       <c r="D91">
-        <v>26.93620786157238</v>
+        <v>26.7754842061009</v>
       </c>
       <c r="E91">
-        <v>48.08000000000001</v>
+        <v>48.9</v>
       </c>
       <c r="F91">
-        <v>72.98</v>
+        <v>73.8</v>
       </c>
       <c r="G91">
         <v>31.9</v>
@@ -8743,37 +8743,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M91">
-        <v>17.208684</v>
+        <v>17.40204</v>
       </c>
       <c r="N91">
-        <v>-10.468684</v>
+        <v>-10.66204</v>
       </c>
       <c r="O91">
-        <v>-3.140605200000001</v>
+        <v>-3.198612</v>
       </c>
       <c r="P91">
-        <v>-7.328078800000002</v>
+        <v>-7.463428</v>
       </c>
       <c r="Q91">
-        <v>-2.468078800000002</v>
+        <v>-2.603428</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.1953945414180424</v>
+        <v>0.2103539955598467</v>
       </c>
       <c r="T91">
-        <v>3.454839293719226</v>
+        <v>3.800323223091149</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1174988162953076</v>
+        <v>0.1161932738920264</v>
       </c>
       <c r="W91">
-        <v>0.2080937791175665</v>
+        <v>0.2084016260162602</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3916627209843587</v>
+        <v>0.3873109129734215</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2085968629706188</v>
+        <v>0.2104968629706188</v>
       </c>
       <c r="C92">
-        <v>-15.12451579389911</v>
+        <v>-16.1033328059256</v>
       </c>
       <c r="D92">
-        <v>26.7754842061009</v>
+        <v>26.6166671940744</v>
       </c>
       <c r="E92">
-        <v>48.9</v>
+        <v>49.72000000000001</v>
       </c>
       <c r="F92">
-        <v>73.8</v>
+        <v>74.62</v>
       </c>
       <c r="G92">
         <v>31.9</v>
@@ -8825,37 +8825,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M92">
-        <v>17.40204</v>
+        <v>17.595396</v>
       </c>
       <c r="N92">
-        <v>-10.66204</v>
+        <v>-10.855396</v>
       </c>
       <c r="O92">
-        <v>-3.198612</v>
+        <v>-3.2566188</v>
       </c>
       <c r="P92">
-        <v>-7.463428</v>
+        <v>-7.598777200000002</v>
       </c>
       <c r="Q92">
-        <v>-2.603428</v>
+        <v>-2.738777200000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2103539955598467</v>
+        <v>0.2286377728442741</v>
       </c>
       <c r="T92">
-        <v>3.800323223091149</v>
+        <v>4.222581358990166</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1161932738920264</v>
+        <v>0.1149164247283778</v>
       </c>
       <c r="W92">
-        <v>0.2084016260162602</v>
+        <v>0.2087027070490485</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3873109129734215</v>
+        <v>0.3830547490945926</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2104968629706188</v>
+        <v>0.2123968629706188</v>
       </c>
       <c r="C93">
-        <v>-16.1033328059256</v>
+        <v>-17.08027690184377</v>
       </c>
       <c r="D93">
-        <v>26.6166671940744</v>
+        <v>26.45972309815623</v>
       </c>
       <c r="E93">
-        <v>49.72000000000001</v>
+        <v>50.54</v>
       </c>
       <c r="F93">
-        <v>74.62</v>
+        <v>75.44</v>
       </c>
       <c r="G93">
         <v>31.9</v>
@@ -8907,37 +8907,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M93">
-        <v>17.595396</v>
+        <v>17.788752</v>
       </c>
       <c r="N93">
-        <v>-10.855396</v>
+        <v>-11.048752</v>
       </c>
       <c r="O93">
-        <v>-3.2566188</v>
+        <v>-3.3146256</v>
       </c>
       <c r="P93">
-        <v>-7.598777200000002</v>
+        <v>-7.734126400000001</v>
       </c>
       <c r="Q93">
-        <v>-2.738777200000002</v>
+        <v>-2.874126400000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2286377728442741</v>
+        <v>0.2514924944498085</v>
       </c>
       <c r="T93">
-        <v>4.222581358990166</v>
+        <v>4.750404028863938</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1149164247283778</v>
+        <v>0.1136673331552433</v>
       </c>
       <c r="W93">
-        <v>0.2087027070490485</v>
+        <v>0.2089972428419936</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3830547490945926</v>
+        <v>0.3788911105174775</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2123968629706188</v>
+        <v>0.2142968629706188</v>
       </c>
       <c r="C94">
-        <v>-17.08027690184377</v>
+        <v>-18.05538101816585</v>
       </c>
       <c r="D94">
-        <v>26.45972309815623</v>
+        <v>26.30461898183415</v>
       </c>
       <c r="E94">
-        <v>50.54</v>
+        <v>51.36000000000001</v>
       </c>
       <c r="F94">
-        <v>75.44</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="G94">
         <v>31.9</v>
@@ -8989,37 +8989,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M94">
-        <v>17.788752</v>
+        <v>17.982108</v>
       </c>
       <c r="N94">
-        <v>-11.048752</v>
+        <v>-11.242108</v>
       </c>
       <c r="O94">
-        <v>-3.3146256</v>
+        <v>-3.372632400000001</v>
       </c>
       <c r="P94">
-        <v>-7.734126400000001</v>
+        <v>-7.869475600000001</v>
       </c>
       <c r="Q94">
-        <v>-2.874126400000001</v>
+        <v>-3.009475600000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2514924944498085</v>
+        <v>0.2808771365140669</v>
       </c>
       <c r="T94">
-        <v>4.750404028863938</v>
+        <v>5.429033175844501</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1136673331552433</v>
+        <v>0.1124451037664772</v>
       </c>
       <c r="W94">
-        <v>0.2089972428419936</v>
+        <v>0.2092854445318647</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3788911105174775</v>
+        <v>0.3748170125549239</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2142968629706188</v>
+        <v>0.2161968629706188</v>
       </c>
       <c r="C95">
-        <v>-18.05538101816585</v>
+        <v>-19.02867732362323</v>
       </c>
       <c r="D95">
-        <v>26.30461898183415</v>
+        <v>26.15132267637677</v>
       </c>
       <c r="E95">
-        <v>51.36000000000001</v>
+        <v>52.18</v>
       </c>
       <c r="F95">
-        <v>76.26000000000001</v>
+        <v>77.08</v>
       </c>
       <c r="G95">
         <v>31.9</v>
@@ -9071,37 +9071,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M95">
-        <v>17.982108</v>
+        <v>18.175464</v>
       </c>
       <c r="N95">
-        <v>-11.242108</v>
+        <v>-11.435464</v>
       </c>
       <c r="O95">
-        <v>-3.372632400000001</v>
+        <v>-3.430639200000001</v>
       </c>
       <c r="P95">
-        <v>-7.869475600000001</v>
+        <v>-8.004824800000002</v>
       </c>
       <c r="Q95">
-        <v>-3.009475600000001</v>
+        <v>-3.144824800000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.2808771365140669</v>
+        <v>0.3200566592664114</v>
       </c>
       <c r="T95">
-        <v>5.429033175844501</v>
+        <v>6.333872038485254</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1124451037664772</v>
+        <v>0.1112488792583232</v>
       </c>
       <c r="W95">
-        <v>0.2092854445318647</v>
+        <v>0.2095675142708874</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3748170125549239</v>
+        <v>0.3708295975277439</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2161968629706188</v>
+        <v>0.2180968629706188</v>
       </c>
       <c r="C96">
-        <v>-19.02867732362323</v>
+        <v>-20.00019724140898</v>
       </c>
       <c r="D96">
-        <v>26.15132267637677</v>
+        <v>25.99980275859102</v>
       </c>
       <c r="E96">
-        <v>52.18</v>
+        <v>53.00000000000001</v>
       </c>
       <c r="F96">
-        <v>77.08</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G96">
         <v>31.9</v>
@@ -9153,37 +9153,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M96">
-        <v>18.175464</v>
+        <v>18.36882</v>
       </c>
       <c r="N96">
-        <v>-11.435464</v>
+        <v>-11.62882</v>
       </c>
       <c r="O96">
-        <v>-3.430639200000001</v>
+        <v>-3.488646000000001</v>
       </c>
       <c r="P96">
-        <v>-8.004824800000002</v>
+        <v>-8.140174000000004</v>
       </c>
       <c r="Q96">
-        <v>-3.144824800000001</v>
+        <v>-3.280174000000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3200566592664114</v>
+        <v>0.3749079911196939</v>
       </c>
       <c r="T96">
-        <v>6.333872038485254</v>
+        <v>7.600646446182307</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1112488792583232</v>
+        <v>0.110077838424025</v>
       </c>
       <c r="W96">
-        <v>0.2095675142708874</v>
+        <v>0.2098436456996149</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3708295975277439</v>
+        <v>0.3669261280800834</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2180968629706188</v>
+        <v>0.2199968629706189</v>
       </c>
       <c r="C97">
-        <v>-20.00019724140898</v>
+        <v>-20.96997147065149</v>
       </c>
       <c r="D97">
-        <v>25.99980275859102</v>
+        <v>25.85002852934852</v>
       </c>
       <c r="E97">
-        <v>53.00000000000001</v>
+        <v>53.82000000000001</v>
       </c>
       <c r="F97">
-        <v>77.90000000000001</v>
+        <v>78.72000000000001</v>
       </c>
       <c r="G97">
         <v>31.9</v>
@@ -9235,37 +9235,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M97">
-        <v>18.36882</v>
+        <v>18.562176</v>
       </c>
       <c r="N97">
-        <v>-11.62882</v>
+        <v>-11.82217600000001</v>
       </c>
       <c r="O97">
-        <v>-3.488646000000001</v>
+        <v>-3.546652800000002</v>
       </c>
       <c r="P97">
-        <v>-8.140174000000004</v>
+        <v>-8.275523200000004</v>
       </c>
       <c r="Q97">
-        <v>-3.280174000000003</v>
+        <v>-3.415523200000004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.3749079911196939</v>
+        <v>0.4571849888996175</v>
       </c>
       <c r="T97">
-        <v>7.600646446182307</v>
+        <v>9.500808057727889</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.110077838424025</v>
+        <v>0.1089311942737748</v>
       </c>
       <c r="W97">
-        <v>0.2098436456996149</v>
+        <v>0.2101140243902439</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3669261280800834</v>
+        <v>0.3631039809125824</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2199968629706188</v>
+        <v>0.2218968629706188</v>
       </c>
       <c r="C98">
-        <v>-20.96997147065147</v>
+        <v>-21.9380300071502</v>
       </c>
       <c r="D98">
-        <v>25.85002852934852</v>
+        <v>25.70196999284979</v>
       </c>
       <c r="E98">
-        <v>53.82</v>
+        <v>54.63999999999999</v>
       </c>
       <c r="F98">
-        <v>78.72</v>
+        <v>79.53999999999999</v>
       </c>
       <c r="G98">
         <v>31.9</v>
@@ -9317,37 +9317,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M98">
-        <v>18.562176</v>
+        <v>18.755532</v>
       </c>
       <c r="N98">
-        <v>-11.822176</v>
+        <v>-12.015532</v>
       </c>
       <c r="O98">
-        <v>-3.546652800000001</v>
+        <v>-3.6046596</v>
       </c>
       <c r="P98">
-        <v>-8.275523200000002</v>
+        <v>-8.410872400000001</v>
       </c>
       <c r="Q98">
-        <v>-3.415523200000002</v>
+        <v>-3.5508724</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.4571849888996164</v>
+        <v>0.5943133185328218</v>
       </c>
       <c r="T98">
-        <v>9.500808057727863</v>
+        <v>12.66774407697048</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1089311942737748</v>
+        <v>0.1078081922709524</v>
       </c>
       <c r="W98">
-        <v>0.2101140243902439</v>
+        <v>0.2103788282625094</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3631039809125826</v>
+        <v>0.3593606409031745</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2218968629706188</v>
+        <v>0.2237968629706188</v>
       </c>
       <c r="C99">
-        <v>-21.9380300071502</v>
+        <v>-22.904402163403</v>
       </c>
       <c r="D99">
-        <v>25.70196999284979</v>
+        <v>25.555597836597</v>
       </c>
       <c r="E99">
-        <v>54.63999999999999</v>
+        <v>55.46</v>
       </c>
       <c r="F99">
-        <v>79.53999999999999</v>
+        <v>80.36</v>
       </c>
       <c r="G99">
         <v>31.9</v>
@@ -9399,37 +9399,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M99">
-        <v>18.755532</v>
+        <v>18.948888</v>
       </c>
       <c r="N99">
-        <v>-12.015532</v>
+        <v>-12.208888</v>
       </c>
       <c r="O99">
-        <v>-3.6046596</v>
+        <v>-3.6626664</v>
       </c>
       <c r="P99">
-        <v>-8.410872400000001</v>
+        <v>-8.546221600000001</v>
       </c>
       <c r="Q99">
-        <v>-3.5508724</v>
+        <v>-3.686221600000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.5943133185328218</v>
+        <v>0.8685699777992327</v>
       </c>
       <c r="T99">
-        <v>12.66774407697048</v>
+        <v>19.00161611545573</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1078081922709524</v>
+        <v>0.1067081086763508</v>
       </c>
       <c r="W99">
-        <v>0.2103788282625094</v>
+        <v>0.2106382279741165</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3593606409031745</v>
+        <v>0.355693695587836</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2237968629706188</v>
+        <v>0.2256968629706188</v>
       </c>
       <c r="C100">
-        <v>-22.904402163403</v>
+        <v>-23.86911658795271</v>
       </c>
       <c r="D100">
-        <v>25.555597836597</v>
+        <v>25.41088341204728</v>
       </c>
       <c r="E100">
-        <v>55.46</v>
+        <v>56.27999999999999</v>
       </c>
       <c r="F100">
-        <v>80.36</v>
+        <v>81.17999999999999</v>
       </c>
       <c r="G100">
         <v>31.9</v>
@@ -9481,37 +9481,37 @@
         <v>6.739999999999999</v>
       </c>
       <c r="M100">
-        <v>18.948888</v>
+        <v>19.142244</v>
       </c>
       <c r="N100">
-        <v>-12.208888</v>
+        <v>-12.402244</v>
       </c>
       <c r="O100">
-        <v>-3.6626664</v>
+        <v>-3.7206732</v>
       </c>
       <c r="P100">
-        <v>-8.546221600000001</v>
+        <v>-8.681570799999999</v>
       </c>
       <c r="Q100">
-        <v>-3.686221600000001</v>
+        <v>-3.821570799999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.8685699777992327</v>
+        <v>1.691339955598466</v>
       </c>
       <c r="T100">
-        <v>19.00161611545573</v>
+        <v>38.00323223091145</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1067081086763508</v>
+        <v>0.1056302489927513</v>
       </c>
       <c r="W100">
-        <v>0.2106382279741165</v>
+        <v>0.2108923872875093</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.355693695587836</v>
+        <v>0.3521008299758377</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2256968629706188</v>
-      </c>
-      <c r="C101">
-        <v>-23.86911658795271</v>
-      </c>
-      <c r="D101">
-        <v>25.41088341204728</v>
-      </c>
-      <c r="E101">
-        <v>56.27999999999999</v>
-      </c>
-      <c r="F101">
-        <v>81.17999999999999</v>
-      </c>
-      <c r="G101">
-        <v>31.9</v>
-      </c>
-      <c r="H101">
-        <v>57.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>11.6</v>
-      </c>
-      <c r="K101">
-        <v>4.86</v>
-      </c>
-      <c r="L101">
-        <v>6.739999999999999</v>
-      </c>
-      <c r="M101">
-        <v>19.142244</v>
-      </c>
-      <c r="N101">
-        <v>-12.402244</v>
-      </c>
-      <c r="O101">
-        <v>-3.7206732</v>
-      </c>
-      <c r="P101">
-        <v>-8.681570799999999</v>
-      </c>
-      <c r="Q101">
-        <v>-3.821570799999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.691339955598466</v>
-      </c>
-      <c r="T101">
-        <v>38.00323223091145</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1056302489927513</v>
-      </c>
-      <c r="W101">
-        <v>0.2108923872875093</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3521008299758377</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
